--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,18 +635,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,17 +958,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1062,17 +1062,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,39 +1155,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>75.44</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1210,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,7 +1259,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1282,22 +1274,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1322,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1362,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,31 +1371,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,92 +1483,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.0925</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dundee United vs Rangers FC</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Dundee United</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Rangers FC</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>L19228047</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526560</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>51.909968</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,110 +1587,222 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,17 +750,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,17 +958,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1059,23 +1059,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1083,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,17 +1174,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1187,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1232,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,12 +1267,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1274,22 +1282,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1299,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,12 +1379,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1386,22 +1394,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1411,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,28 +1491,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1515,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,12 +1595,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1602,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1627,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,110 +1707,1718 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>37.20755</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.5925</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785598183</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>62.797553</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>253.59</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.5925</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785598181</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>428.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785597811</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>48.165517</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>118.87998</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.9175</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19228045</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785597330</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785781800</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>129.56946</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.5837</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785543200</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.713062</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>40.29346</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785529916</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>90.293468</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785529915</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2.577031</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785529816</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2.754491</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785529105</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.2612</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>6.77512</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +651,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -786,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -890,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,23 +979,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -971,7 +1007,11 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -994,7 +1034,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,39 +1091,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1106,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,23 +1195,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1187,7 +1223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1240,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1282,12 +1322,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1297,24 +1337,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1322,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,12 +1419,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1394,22 +1434,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1434,7 +1474,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1504,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1514,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,23 +1531,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1515,7 +1559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1538,7 +1586,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,12 +1643,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1610,39 +1658,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1650,7 +1698,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1728,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1738,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,12 +1755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1722,22 +1770,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1762,7 +1810,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1840,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1850,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,12 +1867,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1834,22 +1882,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,7 +1922,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1952,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1962,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,28 +1979,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1978,7 +2026,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2056,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2066,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,67 +2083,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2160,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2187,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,17 +2198,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2194,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,28 +2291,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2283,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2328,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,7 +2395,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2366,17 +2406,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2387,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2472,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2467,23 +2507,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2491,27 +2539,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2584,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2574,17 +2622,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2595,27 +2643,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2688,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2675,23 +2723,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2699,27 +2755,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2744,17 +2800,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,23 +2827,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2795,7 +2855,11 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2803,27 +2867,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2848,17 +2912,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,39 +2939,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2915,27 +2971,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2960,17 +3016,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,12 +3043,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3002,22 +3058,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3027,27 +3083,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,17 +3128,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3107,23 +3163,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3131,27 +3195,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,17 +3240,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,12 +3267,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3218,22 +3282,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Aberdeen +0.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3243,27 +3307,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3288,17 +3352,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,110 +3379,1494 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785597811</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>48.165517</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>118.87998</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.9175</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19228045</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785597330</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785781800</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>129.56946</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.5837</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785543200</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.713062</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>40.29346</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785529916</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>90.293468</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785529915</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2.577031</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785529816</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2.754491</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785529105</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.2612</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>6.77512</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,39 +762,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -810,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,39 +986,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1034,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1099,23 +1091,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,62 +1195,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1299,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,7 +1314,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1392,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,12 +1411,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1434,39 +1426,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1474,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1504,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,17 +1538,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1586,7 +1578,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1616,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,7 +1635,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1658,22 +1650,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1698,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1728,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1738,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1770,39 +1762,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1810,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1840,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1850,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,7 +1859,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1882,22 +1874,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1922,7 +1914,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1962,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1979,31 +1971,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,28 +2083,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,23 +2187,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,7 +2395,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2406,17 +2406,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2507,31 +2507,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2554,7 +2546,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2594,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2619,23 +2611,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2723,19 +2723,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2743,26 +2739,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2770,7 +2762,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2800,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,12 +2819,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2842,22 +2834,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2882,7 +2874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2912,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,7 +2931,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2947,23 +2939,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,27 +3043,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3071,26 +3067,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3098,7 +3090,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3128,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3138,7 +3130,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,12 +3147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3170,22 +3162,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3210,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3240,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3250,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3267,7 +3259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3352,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,36 +3371,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,27 +3483,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3511,11 +3507,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3523,27 +3515,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3560,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,31 +3587,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3627,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,28 +3699,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3731,27 +3731,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,18 +3803,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,7 +3907,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,7 +4011,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4022,17 +4022,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4126,17 +4126,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4219,7 +4219,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4230,17 +4230,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4323,39 +4323,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4378,7 +4370,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4408,7 +4400,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4418,7 +4410,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,7 +4427,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4450,22 +4442,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4490,7 +4482,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4530,7 +4522,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4547,31 +4539,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,39 +4651,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4706,7 +4698,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4736,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526560</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4746,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>51.909968</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4763,110 +4755,222 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,39 +874,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -914,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,39 +1098,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,23 +1203,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1242,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,62 +1307,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,39 +1538,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1650,17 +1650,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,39 +1874,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,31 +2083,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2130,7 +2138,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2160,7 +2168,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2170,7 +2178,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,28 +2195,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2234,7 +2242,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2272,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2282,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,23 +2299,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2368,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,7 +2403,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2406,17 +2414,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2442,7 +2450,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2472,7 +2480,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2482,7 +2490,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,7 +2507,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2510,17 +2518,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2546,7 +2554,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2576,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,7 +2611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2611,31 +2619,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2723,23 +2723,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2762,7 +2770,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2792,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,7 +2827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2827,19 +2835,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2847,26 +2851,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,7 +3043,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3051,23 +3051,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3090,7 +3098,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3120,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,27 +3155,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3175,26 +3179,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,36 +3483,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -3530,7 +3538,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3560,7 +3568,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3570,7 +3578,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,27 +3595,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3615,11 +3619,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3627,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,31 +3699,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3731,27 +3739,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3784,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,28 +3811,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3835,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3880,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,18 +3915,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3984,7 +3992,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3994,7 +4002,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,7 +4019,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4027,7 +4035,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4088,7 +4096,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4098,7 +4106,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,7 +4123,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4126,17 +4134,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4162,7 +4170,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4192,7 +4200,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4202,7 +4210,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4219,7 +4227,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4230,17 +4238,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4266,7 +4274,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4296,7 +4304,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4323,7 +4331,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4334,17 +4342,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4370,7 +4378,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4410,7 +4418,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4427,39 +4435,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4554,22 +4554,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,31 +4651,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4698,7 +4706,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4736,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4746,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,39 +4763,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526560</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>51.909968</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,110 +4867,222 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,31 +539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -986,39 +978,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,12 +1202,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1280,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,23 +1307,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1426,47 +1426,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,62 +1523,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1608,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,12 +1627,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1650,39 +1642,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1690,7 +1682,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1720,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1730,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,12 +1739,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1762,12 +1754,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1777,24 +1769,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1802,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1832,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1874,22 +1866,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1944,7 +1936,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1954,7 +1946,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1986,39 +1978,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2026,7 +2018,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2056,7 +2048,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2066,7 +2058,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2098,22 +2090,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2138,7 +2130,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2168,7 +2160,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2178,7 +2170,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2195,31 +2187,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,31 +2299,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2346,7 +2354,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2376,7 +2384,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,7 +2411,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2414,17 +2422,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2450,7 +2458,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2480,7 +2488,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2498,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,28 +2515,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2554,7 +2562,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2584,7 +2592,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2602,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2622,17 +2630,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2658,7 +2666,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2688,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2723,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2723,31 +2731,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,7 +2827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2838,17 +2838,17 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2946,39 +2946,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,39 +3043,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3098,7 +3090,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3128,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3138,7 +3130,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,23 +3147,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3179,7 +3175,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3274,39 +3274,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,39 +3371,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3426,7 +3418,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3456,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,12 +3475,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3498,22 +3490,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3538,7 +3530,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3568,7 +3560,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3578,7 +3570,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,36 +3587,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,12 +3699,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3714,52 +3714,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3784,17 +3784,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,28 +3811,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,31 +3915,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3947,27 +3955,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3992,17 +4000,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4019,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4030,17 +4038,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4051,27 +4059,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4096,17 +4104,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4123,23 +4131,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4200,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4210,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4227,7 +4235,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4238,17 +4246,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4274,7 +4282,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4304,7 +4312,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4314,7 +4322,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4331,7 +4339,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4342,12 +4350,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4408,7 +4416,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4418,7 +4426,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,7 +4443,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4512,7 +4520,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4539,39 +4547,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,39 +4651,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4706,7 +4698,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4736,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4746,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4763,31 +4755,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,7 +4867,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,110 +4979,326 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +651,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,17 +870,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,39 +963,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1003,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1115,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,52 +1186,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1314,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1339,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,67 +1395,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1531,23 +1507,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1570,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,12 +1611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1642,47 +1626,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1754,47 +1738,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1866,39 +1850,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -1906,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1936,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1978,17 +1962,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2018,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2048,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2058,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,31 +2067,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2130,7 +2106,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2160,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2170,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,12 +2163,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2202,39 +2178,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2242,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2272,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,12 +2275,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2314,22 +2290,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2354,7 +2330,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2384,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2394,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2411,31 +2387,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2458,7 +2442,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2488,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2498,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,31 +2499,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2562,7 +2554,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2592,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,23 +2611,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2643,7 +2639,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,31 +2723,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2770,7 +2778,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2800,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,36 +2835,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -2874,7 +2890,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2904,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,7 +2947,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2939,31 +2955,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2986,7 +2994,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3016,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,28 +3051,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3090,7 +3098,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3120,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3155,46 +3163,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,39 +3259,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3314,7 +3306,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3344,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,28 +3363,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3418,7 +3410,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3448,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3458,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,12 +3467,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3490,39 +3482,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3530,7 +3522,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3560,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3570,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,7 +3579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3595,31 +3587,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3642,7 +3626,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3672,7 +3656,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3682,7 +3666,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,7 +3683,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3714,22 +3698,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3754,7 +3738,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3784,7 +3768,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3794,7 +3778,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,7 +3795,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3819,28 +3803,36 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -3858,7 +3850,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3888,7 +3880,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3898,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,67 +3907,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4000,17 +3984,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,15 +4011,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>1</t>
@@ -4043,7 +4031,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4051,7 +4039,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4074,7 +4066,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4104,7 +4096,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4114,7 +4106,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4131,31 +4123,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4163,27 +4163,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4208,17 +4208,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4243,23 +4243,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4267,27 +4275,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4312,17 +4320,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4339,28 +4347,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4371,27 +4379,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4416,17 +4424,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4443,31 +4451,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4475,27 +4491,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4520,17 +4536,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4547,7 +4563,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4558,17 +4574,17 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4579,27 +4595,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4624,17 +4640,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,28 +4667,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4698,7 +4714,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4744,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4754,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,39 +4771,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4810,7 +4818,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4848,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4858,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,39 +4875,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4990,17 +4990,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,39 +5083,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5138,7 +5130,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5168,7 +5160,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5178,7 +5170,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5195,110 +5187,654 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,26 +555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -654,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,27 +739,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,26 +763,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -802,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,17 +958,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -995,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1078,17 +1062,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1099,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,31 +1163,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1226,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1259,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,31 +1267,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1338,7 +1306,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1336,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1346,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1363,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1406,12 +1374,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1427,27 +1395,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1472,17 +1440,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,39 +1467,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1539,27 +1499,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1544,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,12 +1571,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1626,22 +1586,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1651,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1696,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,67 +1683,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,12 +1787,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1850,22 +1802,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1875,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,27 +1899,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1975,11 +1923,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1987,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,28 +2003,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2091,27 +2035,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,17 +2080,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,19 +2107,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>1</t>
@@ -2183,19 +2123,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2203,27 +2139,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2184,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,12 +2211,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2290,22 +2226,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2315,27 +2251,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,12 +2323,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2402,52 +2338,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2408,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,27 +2435,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2527,11 +2459,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2539,27 +2467,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2584,17 +2512,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2626,12 +2554,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2696,7 +2624,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2706,7 +2634,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,12 +2651,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2738,39 +2666,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -2778,7 +2706,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2808,7 +2736,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2818,7 +2746,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,7 +2763,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,22 +2778,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2890,7 +2818,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2920,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,31 +2875,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2994,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3024,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3034,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,31 +2987,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3098,7 +3042,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3128,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3138,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,28 +3099,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3202,7 +3146,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3176,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3186,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,31 +3203,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3306,7 +3258,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3336,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3346,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,36 +3315,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -3410,7 +3370,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3440,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3450,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,12 +3427,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3482,22 +3442,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3522,7 +3482,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,23 +3539,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3603,7 +3567,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3626,7 +3594,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3656,7 +3624,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3666,7 +3634,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3683,12 +3651,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3698,39 +3666,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3738,7 +3706,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3768,7 +3736,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3778,7 +3746,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3795,12 +3763,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3810,22 +3778,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3850,7 +3818,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3880,7 +3848,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3890,7 +3858,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,31 +3875,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3954,7 +3930,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3984,7 +3960,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3994,7 +3970,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,54 +3987,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -4066,7 +4034,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4096,7 +4064,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4106,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4123,39 +4091,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4178,7 +4138,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4208,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4218,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4243,31 +4203,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4290,7 +4242,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4320,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4330,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4347,28 +4299,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4394,7 +4346,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4424,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4434,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4451,27 +4403,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4479,11 +4427,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4491,27 +4435,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4536,17 +4480,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4563,7 +4507,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4571,23 +4515,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4610,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4640,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4650,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4667,28 +4619,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4699,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4744,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4771,7 +4723,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4779,23 +4731,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4803,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4848,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4875,31 +4835,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4907,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4952,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,28 +4947,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5011,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5056,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,31 +5051,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5115,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5160,17 +5136,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5187,7 +5163,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5195,23 +5171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5219,27 +5203,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5264,17 +5248,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,12 +5275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5306,22 +5290,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Aberdeen +0.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5331,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5376,17 +5360,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,39 +5387,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5443,27 +5419,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5488,17 +5464,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,31 +5491,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5547,27 +5531,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5592,17 +5576,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5619,39 +5603,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5659,27 +5635,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5704,17 +5680,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5731,110 +5707,1174 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>40.29346</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785529916</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>90.293468</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785529915</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2.577031</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785529816</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2.754491</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785529105</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.2612</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>6.77512</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -763,7 +783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -771,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +867,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -867,7 +895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -875,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1024,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1051,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1059,15 +1091,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1075,7 +1111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1098,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,12 +1206,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1336,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1374,7 +1414,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1440,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1450,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1478,12 +1518,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1544,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1554,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1571,27 +1611,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1599,26 +1635,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -1626,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1656,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1666,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1694,12 +1726,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1715,27 +1747,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1792,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,27 +1819,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1815,26 +1843,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -1842,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,17 +1934,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1931,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1976,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2014,17 +2038,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2035,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,17 +2142,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2139,27 +2163,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2184,17 +2208,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2219,11 +2243,7 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>10</t>
@@ -2231,19 +2251,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2266,7 +2282,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2296,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2306,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,7 +2339,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2331,31 +2347,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2378,7 +2386,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2408,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,23 +2443,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2459,7 +2471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2467,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2512,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,39 +2555,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2579,27 +2587,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,17 +2632,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,12 +2659,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2666,22 +2674,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2691,27 +2699,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2736,17 +2744,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2763,27 +2771,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2791,11 +2795,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2803,27 +2803,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,39 +2875,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2915,27 +2907,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2960,17 +2952,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,67 +2979,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,17 +3056,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,31 +3083,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3131,27 +3123,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,17 +3168,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,12 +3195,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3218,22 +3210,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3243,27 +3235,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3288,17 +3280,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,27 +3307,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3343,11 +3331,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3355,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3400,17 +3384,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3411,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3442,39 +3426,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3482,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3512,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,12 +3523,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3554,39 +3538,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3594,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3624,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3634,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3666,22 +3650,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3706,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3736,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,7 +3747,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3778,39 +3762,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -3818,7 +3802,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3848,7 +3832,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3842,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,7 +3859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3890,22 +3874,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3930,7 +3914,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3960,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +3954,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,28 +3971,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4034,7 +4018,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4064,7 +4048,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4074,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,31 +4075,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4138,7 +4130,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4168,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,31 +4187,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,31 +4299,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4346,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4376,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,36 +4411,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -4450,7 +4466,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4480,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,12 +4523,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4522,22 +4538,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4562,7 +4578,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4592,7 +4608,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4618,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,31 +4635,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4666,7 +4690,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4720,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4730,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,12 +4747,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4738,7 +4762,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4748,29 +4772,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -4778,7 +4802,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4808,7 +4832,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4842,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,39 +4859,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4890,7 +4906,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4936,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4946,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4963,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4958,17 +4974,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4994,7 +5010,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5040,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5050,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,54 +5067,46 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -5106,7 +5114,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5136,7 +5144,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5154,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,7 +5171,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5171,31 +5179,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5283,31 +5283,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5330,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,36 +5379,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,67 +5491,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5576,17 +5568,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,7 +5595,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5611,15 +5603,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5627,7 +5623,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,31 +5707,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5739,27 +5747,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5784,17 +5792,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5811,28 +5819,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5843,27 +5851,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5888,17 +5896,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5915,31 +5923,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5947,27 +5963,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5992,17 +6008,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6019,7 +6035,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6027,23 +6043,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6051,27 +6075,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6096,17 +6120,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6131,23 +6155,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6155,27 +6187,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6200,17 +6232,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6227,28 +6259,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6259,27 +6291,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6304,17 +6336,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6331,12 +6363,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6346,22 +6378,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6371,27 +6403,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6416,17 +6448,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6443,39 +6475,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6483,27 +6507,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6528,17 +6552,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,28 +6579,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6602,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6632,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6642,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6659,39 +6683,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6714,7 +6730,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6744,7 +6760,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6754,7 +6770,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6771,110 +6787,966 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785529816</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2.754491</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785529105</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.2612</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>6.77512</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,27 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,11 +659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,12 +754,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,19 +859,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -895,11 +875,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -907,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,23 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1056,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,27 +1059,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1111,26 +1083,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -1138,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,23 +1163,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1272,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,23 +1267,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1376,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1414,12 +1382,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1480,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,28 +1475,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1539,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,23 +1579,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1658,7 +1626,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1656,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1666,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1683,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1762,7 +1730,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1760,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1770,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,23 +1787,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1866,7 +1834,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1864,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1874,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1891,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1934,12 +1902,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2000,7 +1968,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +1978,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,7 +1995,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2038,12 +2006,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2104,7 +2072,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2114,7 +2082,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,7 +2099,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2142,12 +2110,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2208,7 +2176,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2218,7 +2186,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2203,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2246,12 +2214,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2312,7 +2280,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2290,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,7 +2307,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,12 +2318,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2416,7 +2384,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2394,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,27 +2411,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2471,26 +2435,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -2498,7 +2458,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2528,7 +2488,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2498,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,7 +2515,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2566,12 +2526,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2587,27 +2547,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2632,17 +2592,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,12 +2619,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2674,12 +2634,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2689,24 +2649,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -2714,7 +2674,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2704,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2714,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,59 +2731,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2848,17 +2816,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,7 +2843,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2883,51 +2851,59 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2952,17 +2928,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +2955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2987,23 +2963,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3011,27 +2995,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3056,17 +3040,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,7 +3067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3098,22 +3082,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3138,7 +3122,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3152,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3162,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,7 +3179,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3203,31 +3187,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3250,7 +3226,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3280,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,7 +3283,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3315,15 +3291,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3331,7 +3311,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3339,27 +3323,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3384,17 +3368,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,12 +3395,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3426,22 +3410,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3451,27 +3435,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3496,17 +3480,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,19 +3507,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>5</t>
@@ -3543,19 +3523,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3563,27 +3539,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3608,17 +3584,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,7 +3611,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3643,59 +3619,51 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3720,17 +3688,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,12 +3715,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3762,22 +3730,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3787,27 +3755,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3832,17 +3800,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,12 +3827,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3874,52 +3842,52 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3944,17 +3912,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,7 +3939,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3979,23 +3947,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4003,27 +3979,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4048,17 +4024,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,12 +4051,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4090,12 +4066,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4105,7 +4081,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4115,27 +4091,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4160,17 +4136,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,27 +4163,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4215,11 +4187,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4227,27 +4195,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4272,17 +4240,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,12 +4267,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4314,52 +4282,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4384,17 +4352,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,27 +4379,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4439,11 +4403,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4451,27 +4411,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4496,17 +4456,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,39 +4483,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4563,27 +4515,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4608,17 +4560,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4635,67 +4587,59 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4720,17 +4664,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4747,39 +4691,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4787,27 +4723,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4832,17 +4768,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4859,7 +4795,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4870,17 +4806,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4891,27 +4827,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4936,17 +4872,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4963,28 +4899,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4995,27 +4931,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5040,17 +4976,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,7 +5003,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5078,17 +5014,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5099,27 +5035,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5144,17 +5080,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,7 +5107,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5182,17 +5118,17 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5203,27 +5139,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5248,17 +5184,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,7 +5211,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5286,17 +5222,17 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5307,27 +5243,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5352,17 +5288,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,7 +5315,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5387,31 +5323,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5419,27 +5347,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5464,17 +5392,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,7 +5419,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5502,12 +5430,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5523,27 +5451,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5568,17 +5496,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,7 +5523,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5603,19 +5531,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5623,11 +5547,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5635,27 +5555,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5680,17 +5600,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5627,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,22 +5642,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5747,27 +5667,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5792,17 +5712,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,23 +5739,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5851,27 +5771,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5896,17 +5816,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5923,12 +5843,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5938,12 +5858,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5953,7 +5873,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5963,27 +5883,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6008,17 +5928,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,7 +5955,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6043,31 +5963,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6075,27 +5987,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6120,17 +6032,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,7 +6059,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6155,31 +6067,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6187,27 +6091,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6232,17 +6136,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6259,28 +6163,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6291,27 +6195,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6336,17 +6240,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6363,12 +6267,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6378,52 +6282,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6448,17 +6352,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6475,7 +6379,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6483,23 +6387,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6507,27 +6419,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6552,17 +6464,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6579,28 +6491,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6611,27 +6523,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6656,17 +6568,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6683,31 +6595,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6715,27 +6635,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6760,17 +6680,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6787,23 +6707,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6811,7 +6735,11 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6819,27 +6747,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6864,17 +6792,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,31 +6819,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6923,27 +6859,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6968,17 +6904,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6995,31 +6931,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7027,27 +6971,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7072,17 +7016,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7099,31 +7043,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7131,27 +7083,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7176,17 +7128,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7203,7 +7155,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7211,31 +7163,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7243,27 +7187,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7288,17 +7232,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7315,12 +7259,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7330,22 +7274,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7355,27 +7299,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7400,17 +7344,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7427,31 +7371,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7459,27 +7411,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7504,17 +7456,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,7 +7483,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7546,22 +7498,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7571,27 +7523,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7616,17 +7568,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,110 +7595,3342 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>58.43</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.1062</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785604011</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>549.929412</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1142.73999</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785604008</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1533.879181</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>79.19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785604004</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>570.738739</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>238.03781</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.3262</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785604004</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>729.617808</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>221.54</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.4112</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785603521</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>538.699088</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>40.12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785603172</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>77.902913</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18.89</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.4075</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785602480</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>46.355828</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785602424</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>11.482759</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.5663</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785600627</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>14.092715</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>15.35</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785600627</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>48.537549</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10.08</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.6025</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785600583</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>16.73029</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.3262</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785600448</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>30.651341</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.3162</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785600138</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>22.513834</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>622.70999</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.5962</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785599983</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1044.377342</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.3275</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785598284</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>3.053435</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>37.20755</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5925</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785598183</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>62.797553</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>253.59</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.5925</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785598181</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>428.0</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785597811</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>48.165517</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>118.87998</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.9175</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19228045</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785597330</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785781800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>129.56946</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.5837</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19228039</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785543200</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785601800</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1.713062</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>40.29346</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785529916</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>90.293468</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785529915</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2.577031</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785529816</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2.754491</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1785529105</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.2612</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>6.77512</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1785529104</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1.587302</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
+          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>19.5311</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0675</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785682854</t>
+          <t>1785727225</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>289.34963</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +654,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785682817</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,19 +755,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -767,26 +771,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785682785</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31.635443</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,23 +851,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>93.10524</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -875,7 +879,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785682784</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>122.105233</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +974,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.4284</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785682781</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>129.298391</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,18 +1067,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1136,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785682739</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>6.568131</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,18 +1171,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.4816</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1240,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785682735</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>25.591593</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,18 +1275,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.60848</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1344,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785682733</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6.053833</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,18 +1379,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>92.46597</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1448,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785681750</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>121.46597</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,28 +1483,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32.47659</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (6.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1507,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785681479</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>61.276585</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1611,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785680616</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.446301</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,28 +1691,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>139.68586</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1730,7 +1738,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1760,7 +1768,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1770,7 +1778,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>409.335853</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1798,17 +1806,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>122.41894</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1834,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1874,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>233.178933</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,23 +1899,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1938,7 +1946,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1968,7 +1976,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785680318</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1978,7 +1986,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.34002</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,7 +2003,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,12 +2014,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>168.68</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2072,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785680305</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2082,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>228.331641</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2099,7 +2107,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2110,12 +2118,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2176,7 +2184,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785678530</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2186,7 +2194,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>27.667233</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2203,7 +2211,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2214,7 +2222,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.31885</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2280,7 +2288,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785678083</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>62.911851</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2307,7 +2315,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2318,12 +2326,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.66999</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785677996</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>55.33332</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2411,7 +2419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2422,7 +2430,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12.42999</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785677920</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2498,7 +2506,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16.911551</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2515,7 +2523,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2526,7 +2534,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.12999</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2592,7 +2600,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785677881</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2602,7 +2610,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.537401</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2619,7 +2627,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2627,19 +2635,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2647,11 +2651,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785677338</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>39.154185</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2746,22 +2746,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55.11998</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785677298</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>73.86262</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785675836</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.546256</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785675803</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>9.057269</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,7 +3067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.524229</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3187,15 +3187,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3203,7 +3207,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3226,7 +3234,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3266,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3.757303</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,7 +3291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3291,19 +3299,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3311,11 +3315,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785672902</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>59.806167</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,7 +3395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3435,27 +3435,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3480,17 +3480,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785672780</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20.675676</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,31 +3507,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3539,27 +3547,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3584,17 +3592,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785672554</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3611,23 +3619,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29.66982</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3688,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785672525</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>53.57981</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3715,27 +3723,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3743,11 +3747,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3755,27 +3755,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,23 +4163,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4187,7 +4191,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4195,27 +4203,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4240,17 +4248,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4267,7 +4275,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4275,19 +4283,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4295,26 +4299,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4379,7 +4379,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4387,15 +4387,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4403,7 +4407,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4426,7 +4434,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4456,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4466,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4483,7 +4491,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4494,7 +4502,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4560,7 +4568,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4570,7 +4578,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4587,7 +4595,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4598,12 +4606,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4664,7 +4672,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4691,7 +4699,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4702,12 +4710,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4778,7 +4786,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4795,7 +4803,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4806,7 +4814,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4872,7 +4880,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4882,7 +4890,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4899,7 +4907,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4910,12 +4918,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4976,7 +4984,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4986,7 +4994,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5003,7 +5011,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5014,12 +5022,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5080,7 +5088,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5090,7 +5098,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5107,7 +5115,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,12 +5126,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5184,7 +5192,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5211,7 +5219,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5222,7 +5230,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5288,7 +5296,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5298,7 +5306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5315,7 +5323,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5326,12 +5334,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5392,7 +5400,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5402,7 +5410,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5419,7 +5427,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5430,12 +5438,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5496,7 +5504,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5506,7 +5514,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5523,7 +5531,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5534,7 +5542,7 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5600,7 +5608,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5610,7 +5618,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5627,27 +5635,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5655,26 +5659,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5739,23 +5739,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5763,7 +5767,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5771,27 +5779,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5816,17 +5824,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5843,27 +5851,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5871,11 +5875,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5883,27 +5883,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5928,17 +5928,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5955,59 +5955,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6032,17 +6040,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6059,7 +6067,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6070,7 +6078,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6146,7 +6154,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6163,7 +6171,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6174,17 +6182,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6210,7 +6218,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6240,7 +6248,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6250,7 +6258,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6267,7 +6275,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6275,31 +6283,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6307,27 +6307,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6499,23 +6499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6523,27 +6531,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6568,17 +6576,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6595,39 +6603,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6635,27 +6635,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6707,12 +6707,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6722,22 +6722,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6819,12 +6819,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6834,39 +6834,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6946,22 +6946,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7058,39 +7058,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7163,23 +7163,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7202,7 +7210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7232,7 +7240,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7242,7 +7250,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7259,62 +7267,54 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7371,12 +7371,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7483,12 +7483,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7498,39 +7498,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7610,17 +7610,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7707,7 +7707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7834,39 +7834,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7931,7 +7931,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7946,22 +7946,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8043,31 +8043,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8090,7 +8098,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8120,7 +8128,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8130,7 +8138,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8147,28 +8155,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8194,7 +8202,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8224,7 +8232,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8234,7 +8242,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8251,23 +8259,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8328,7 +8336,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8338,7 +8346,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8355,7 +8363,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8366,17 +8374,17 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8402,7 +8410,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8432,7 +8440,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8442,7 +8450,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8459,7 +8467,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8470,17 +8478,17 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8506,7 +8514,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8536,7 +8544,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8546,7 +8554,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8563,7 +8571,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8571,31 +8579,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8675,7 +8675,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8683,23 +8683,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8722,7 +8730,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8752,7 +8760,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8762,7 +8770,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8779,7 +8787,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8787,19 +8795,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8807,26 +8811,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8891,12 +8891,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9003,7 +9003,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9011,23 +9011,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9050,7 +9058,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9080,7 +9088,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9090,7 +9098,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9107,27 +9115,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9135,26 +9139,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9219,12 +9219,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9234,22 +9234,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9331,7 +9331,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9443,36 +9443,44 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -9490,7 +9498,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9520,7 +9528,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9530,7 +9538,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9547,27 +9555,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9575,11 +9579,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9587,27 +9587,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9632,17 +9632,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9659,31 +9659,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9691,27 +9699,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9736,17 +9744,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9763,28 +9771,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -9795,27 +9803,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9840,17 +9848,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9867,18 +9875,18 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9944,7 +9952,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9954,7 +9962,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9971,7 +9979,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9987,7 +9995,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10048,7 +10056,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10058,7 +10066,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10075,7 +10083,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10086,17 +10094,17 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -10122,7 +10130,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10152,7 +10160,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10162,7 +10170,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10179,7 +10187,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10190,17 +10198,17 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10226,7 +10234,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10256,7 +10264,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10266,7 +10274,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10283,7 +10291,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10294,17 +10302,17 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -10330,7 +10338,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10370,7 +10378,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10387,39 +10395,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10499,7 +10499,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10514,22 +10514,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10611,31 +10611,39 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10658,7 +10666,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10688,7 +10696,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10698,7 +10706,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10715,39 +10723,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526560</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>51.909968</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10827,110 +10827,222 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="V99" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
+          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.5311</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0675</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,32 +561,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785727225</t>
+          <t>1785747031</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>289.34963</t>
+          <t>33.684211</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
+          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785682854</t>
+          <t>1785735473</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>9.54652</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
+          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>213.04999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785682817</t>
+          <t>1785734664</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>353.609942</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
+          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -891,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785682785</t>
+          <t>1785734506</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31.635443</t>
+          <t>13.029412</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,23 +963,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
+          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93.10524</t>
+          <t>19.5311</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.0675</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,7 +991,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -995,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785682784</t>
+          <t>1785727225</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>122.105233</t>
+          <t>289.34963</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,23 +1075,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>98.4284</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1114,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785682781</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>129.298391</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,23 +1179,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785682739</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6.568131</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,23 +1283,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.4816</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1299,7 +1311,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1322,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785682735</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>25.591593</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,23 +1395,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.60848</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1456,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785682733</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6.053833</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,18 +1499,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>92.46597</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1560,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785681750</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>121.46597</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,28 +1603,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32.47659</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (6.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1619,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785681479</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>61.276585</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,23 +1707,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1738,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1768,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785680616</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>47.446301</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,28 +1811,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>139.68586</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1842,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1872,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>409.335853</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,23 +1915,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>122.41894</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1946,7 +1962,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>233.178933</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,28 +2019,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2035,27 +2051,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2096,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785680318</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.34002</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,23 +2123,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>168.68</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2154,7 +2170,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2184,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785680305</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2194,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>228.331641</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,28 +2227,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2258,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2288,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785678530</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2298,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>27.667233</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2315,23 +2331,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.31885</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2362,7 +2378,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2392,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785678083</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2402,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>62.911851</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,7 +2435,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2430,12 +2446,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.66999</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2496,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785677996</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2506,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>55.33332</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,7 +2539,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2534,12 +2550,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.42999</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2600,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785677920</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2610,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16.911551</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2627,7 +2643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2638,12 +2654,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.12999</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2704,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785677881</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2714,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.537401</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2731,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2739,19 +2755,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2759,11 +2771,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2786,7 +2794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2816,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785677338</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2826,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>39.154185</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2843,39 +2851,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.11998</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785677298</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>73.86262</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2963,19 +2963,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2983,11 +2979,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3010,7 +3002,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3040,7 +3032,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785675836</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3042,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>4.546256</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,7 +3059,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3075,19 +3067,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3095,11 +3083,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3122,7 +3106,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3152,7 +3136,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785675803</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3162,7 +3146,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>9.057269</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,7 +3163,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3264,7 +3248,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3258,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3.524229</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,31 +3275,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3338,7 +3330,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3368,7 +3360,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3370,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.757303</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,7 +3387,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3410,7 +3402,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3480,7 +3472,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785672902</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3482,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>59.806167</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,7 +3499,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3522,22 +3514,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3547,27 +3539,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3592,17 +3584,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785672780</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20.675676</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,23 +3611,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3643,7 +3639,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785672554</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,23 +3723,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29.66982</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785672525</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>53.57981</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,12 +3827,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3867,27 +3867,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3954,39 +3954,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>St. Johnstone vs Kilmarnock</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>St. Johnstone</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>St. Johnstone vs Kilmarnock</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Kilmarnock</t>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,27 +4051,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4079,11 +4075,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4091,27 +4083,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4136,17 +4128,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,7 +4155,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4171,19 +4163,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4191,11 +4179,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4203,27 +4187,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4248,17 +4232,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,23 +4259,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4299,7 +4287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4307,27 +4299,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4352,17 +4344,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4379,12 +4371,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4394,12 +4386,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4409,7 +4401,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4419,27 +4411,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4464,17 +4456,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,23 +4483,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4515,7 +4511,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4523,27 +4523,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4568,17 +4568,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,23 +4595,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4619,7 +4623,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4627,27 +4635,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4672,17 +4680,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,7 +4707,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4710,12 +4718,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4776,7 +4784,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4786,7 +4794,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4803,7 +4811,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4811,15 +4819,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4827,7 +4839,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4850,7 +4866,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4880,7 +4896,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4890,7 +4906,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4907,7 +4923,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4918,7 +4934,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4984,7 +5000,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4994,7 +5010,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5011,7 +5027,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5022,12 +5038,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5088,7 +5104,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5098,7 +5114,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5115,7 +5131,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5126,12 +5142,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5192,7 +5208,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5202,7 +5218,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5219,7 +5235,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5230,12 +5246,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5296,7 +5312,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5306,7 +5322,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5323,7 +5339,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5334,12 +5350,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5400,7 +5416,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5410,7 +5426,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5427,7 +5443,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5438,12 +5454,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5504,7 +5520,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5514,7 +5530,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,7 +5547,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5542,12 +5558,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5608,7 +5624,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5618,7 +5634,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5635,7 +5651,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5646,7 +5662,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5712,7 +5728,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5722,7 +5738,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5739,27 +5755,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5767,26 +5779,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -5794,7 +5802,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5824,7 +5832,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5834,7 +5842,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5851,7 +5859,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5862,12 +5870,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5883,27 +5891,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5928,17 +5936,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5955,27 +5963,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5983,26 +5987,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6067,7 +6067,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6078,17 +6078,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6099,27 +6099,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6171,59 +6171,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6248,17 +6256,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6275,7 +6283,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6286,17 +6294,17 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6322,7 +6330,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6352,7 +6360,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6362,7 +6370,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6379,12 +6387,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6394,22 +6402,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6464,7 +6472,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6474,7 +6482,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6491,7 +6499,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6499,31 +6507,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6531,27 +6531,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6614,17 +6614,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6707,39 +6707,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6747,27 +6739,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6792,17 +6784,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6819,12 +6811,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6834,12 +6826,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6859,27 +6851,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6904,17 +6896,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6931,12 +6923,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6946,52 +6938,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7016,17 +7008,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7043,39 +7035,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7083,27 +7067,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7128,17 +7112,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7155,7 +7139,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7170,39 +7154,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7210,7 +7194,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7240,7 +7224,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7250,7 +7234,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7267,31 +7251,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7314,7 +7306,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7344,7 +7336,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7354,7 +7346,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7371,12 +7363,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7386,47 +7378,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7456,7 +7448,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7466,7 +7458,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7483,12 +7475,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7498,47 +7490,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7568,7 +7560,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7578,7 +7570,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7595,7 +7587,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7610,12 +7602,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7680,7 +7672,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7690,7 +7682,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7707,7 +7699,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7715,46 +7707,38 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7762,7 +7746,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7792,7 +7776,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7802,7 +7786,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7819,12 +7803,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7834,22 +7818,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7874,7 +7858,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7904,7 +7888,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7914,7 +7898,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7931,12 +7915,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7946,39 +7930,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7986,7 +7970,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8016,7 +8000,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8026,7 +8010,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8043,7 +8027,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8058,22 +8042,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8098,7 +8082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8128,7 +8112,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8138,7 +8122,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8155,31 +8139,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8202,7 +8194,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8232,7 +8224,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8242,7 +8234,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8259,23 +8251,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8283,7 +8279,11 @@
           <t>Under/Over (2)</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8363,31 +8363,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8410,7 +8418,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8440,7 +8448,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8450,7 +8458,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8467,31 +8475,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8514,7 +8530,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8544,7 +8560,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8554,7 +8570,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8571,7 +8587,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8582,17 +8598,17 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8618,7 +8634,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8648,7 +8664,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8658,7 +8674,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8675,39 +8691,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8730,7 +8738,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8760,7 +8768,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8770,7 +8778,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8787,7 +8795,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8798,17 +8806,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8834,7 +8842,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8864,7 +8872,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8874,7 +8882,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8891,7 +8899,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8899,46 +8907,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9003,39 +9003,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9058,7 +9050,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9088,7 +9080,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9098,7 +9090,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9115,31 +9107,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9219,27 +9219,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9247,26 +9243,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -9274,7 +9266,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9304,7 +9296,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9314,7 +9306,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9331,7 +9323,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9346,22 +9338,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9386,7 +9378,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9416,7 +9408,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9426,7 +9418,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9443,12 +9435,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9458,22 +9450,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9498,7 +9490,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9528,7 +9520,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9538,7 +9530,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9555,7 +9547,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9566,17 +9558,17 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9602,7 +9594,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9632,7 +9624,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9642,7 +9634,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9659,12 +9651,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9674,52 +9666,52 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9744,17 +9736,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9771,7 +9763,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9779,23 +9771,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9875,31 +9875,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9907,27 +9915,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9952,17 +9960,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9979,28 +9987,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10011,27 +10019,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -10056,17 +10064,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10083,31 +10091,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10115,27 +10131,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10160,17 +10176,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10187,7 +10203,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10203,12 +10219,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10219,27 +10235,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -10264,17 +10280,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10291,23 +10307,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10368,7 +10384,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10378,7 +10394,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10395,7 +10411,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10406,17 +10422,17 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10442,7 +10458,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10472,7 +10488,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10482,7 +10498,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10499,39 +10515,31 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10554,7 +10562,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10584,7 +10592,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10594,7 +10602,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10611,39 +10619,31 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10723,7 +10723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10734,17 +10734,17 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10827,39 +10827,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10882,7 +10874,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10912,7 +10904,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10922,7 +10914,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10939,110 +10931,550 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>75.44</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.1313</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>574.780952</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>169.77</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1785526843</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1061.0625</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T103" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="U103" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="V103" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
+          <t>0xb72a00c5e8da6d7e2b4252e503b7c2bfc4d447755058015c026369de2fbb14f4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>178.59</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785747031</t>
+          <t>1785767238</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33.684211</t>
+          <t>2857.44</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
+          <t>0x9225eefdc660d0c6bcf7f3eda3ca158d40cc8783d07cf561c29062114d1343f4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>158.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785735473</t>
+          <t>1785767197</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>9.54652</t>
+          <t>2535.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
+          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>213.04999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785734664</t>
+          <t>1785747031</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>353.609942</t>
+          <t>33.684211</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
+          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -906,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
+          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785734506</t>
+          <t>1785735473</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.029412</t>
+          <t>9.54652</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,62 +979,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
+          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.5311</t>
+          <t>213.04999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0675</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785727225</t>
+          <t>1785734664</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>289.34963</t>
+          <t>353.609942</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,28 +1083,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
+          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1107,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785682854</t>
+          <t>1785734506</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>13.029412</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,23 +1187,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
+          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>19.5311</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0675</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1203,7 +1215,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1211,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785682817</t>
+          <t>1785727225</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>289.34963</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,19 +1307,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1311,26 +1323,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -1368,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785682785</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31.635443</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,23 +1403,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>93.10524</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1442,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785682784</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>122.105233</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,23 +1507,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>98.4284</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1523,7 +1535,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1546,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1576,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785682781</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>129.298391</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,23 +1619,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1680,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785682739</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.568131</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1718,7 +1734,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.4816</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1784,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785682735</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>25.591593</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,18 +1827,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.60848</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1888,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785682733</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>6.053833</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,18 +1931,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>92.46597</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1992,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785681750</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>121.46597</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,28 +2035,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32.47659</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (6.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2051,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2112,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785681479</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>61.276585</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,23 +2139,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2170,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2200,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785680616</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>47.446301</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2238,17 +2254,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>139.68586</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2259,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2304,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>409.335853</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,23 +2347,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>122.41894</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2408,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>233.178933</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,28 +2451,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2482,7 +2498,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2512,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785680318</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.34002</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,23 +2555,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>168.68</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2586,7 +2602,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2616,7 +2632,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785680305</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2642,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>228.331641</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,7 +2659,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2654,12 +2670,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2736,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785678530</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2746,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>27.667233</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2763,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,12 +2774,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.31885</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2824,7 +2840,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785678083</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2850,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>62.911851</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,7 +2867,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2862,12 +2878,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>40.66999</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2928,7 +2944,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785677996</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2938,7 +2954,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>55.33332</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,7 +2971,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2966,12 +2982,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.42999</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3032,7 +3048,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785677920</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3042,7 +3058,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16.911551</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3059,7 +3075,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3070,7 +3086,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.12999</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3136,7 +3152,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785677881</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3146,7 +3162,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.537401</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3163,7 +3179,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3171,19 +3187,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3191,11 +3203,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3218,7 +3226,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3248,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785677338</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3258,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>39.154185</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3275,39 +3283,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.11998</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785677298</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>73.86262</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785675836</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.546256</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3514,22 +3514,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785675803</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9.057269</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3.524229</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3731,15 +3731,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3747,7 +3751,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3770,7 +3778,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3800,7 +3808,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3818,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.757303</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,7 +3835,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3842,7 +3850,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785672902</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3922,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>59.806167</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,7 +3947,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3947,31 +3955,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -3979,27 +3979,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785672780</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>20.675676</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,23 +4051,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4075,7 +4079,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4098,7 +4106,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4128,7 +4136,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785672554</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4138,7 +4146,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4155,31 +4163,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29.66982</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4187,27 +4203,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4232,17 +4248,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785672525</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>53.57981</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4259,7 +4275,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4267,11 +4283,7 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>5</t>
@@ -4279,7 +4291,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4287,11 +4299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4299,27 +4307,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4344,17 +4352,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4371,27 +4379,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4399,11 +4403,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4411,27 +4411,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4456,17 +4456,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4483,12 +4483,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,12 +4595,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4707,23 +4707,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4731,7 +4735,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -4739,27 +4747,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4784,17 +4792,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4811,12 +4819,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4826,12 +4834,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4841,7 +4849,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4851,27 +4859,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4896,17 +4904,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4923,7 +4931,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4934,7 +4942,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5000,7 +5008,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5010,7 +5018,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5027,7 +5035,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5035,15 +5043,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5051,7 +5063,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5074,7 +5090,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5104,7 +5120,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5114,7 +5130,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5131,7 +5147,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5142,12 +5158,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5208,7 +5224,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5218,7 +5234,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5235,7 +5251,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5246,7 +5262,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5312,7 +5328,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5322,7 +5338,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5339,7 +5355,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5350,12 +5366,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5416,7 +5432,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5426,7 +5442,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5443,7 +5459,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5454,12 +5470,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5520,7 +5536,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5530,7 +5546,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5547,7 +5563,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5624,7 +5640,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5651,7 +5667,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5662,7 +5678,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5728,7 +5744,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5738,7 +5754,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5755,7 +5771,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5766,12 +5782,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5832,7 +5848,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5842,7 +5858,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5859,7 +5875,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5870,12 +5886,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5936,7 +5952,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5946,7 +5962,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,7 +5979,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5974,7 +5990,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6040,7 +6056,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6050,7 +6066,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6067,7 +6083,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6078,12 +6094,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6144,7 +6160,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6154,7 +6170,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6171,27 +6187,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6199,26 +6211,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -6226,7 +6234,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6256,7 +6264,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6266,7 +6274,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6283,7 +6291,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6294,12 +6302,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6315,27 +6323,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6360,17 +6368,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6387,12 +6395,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6402,7 +6410,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6472,7 +6480,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6482,7 +6490,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6499,7 +6507,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6510,17 +6518,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6546,7 +6554,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6576,7 +6584,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6586,7 +6594,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6603,59 +6611,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6680,17 +6696,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6707,7 +6723,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6718,17 +6734,17 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6754,7 +6770,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6784,7 +6800,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6794,7 +6810,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6811,7 +6827,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6819,31 +6835,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6851,27 +6859,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6896,17 +6904,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6923,7 +6931,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6931,31 +6939,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6963,27 +6963,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7035,7 +7035,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7043,23 +7043,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7067,27 +7075,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7112,17 +7120,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7139,12 +7147,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7154,22 +7162,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7179,27 +7187,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7224,17 +7232,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7251,39 +7259,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7291,27 +7291,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7378,39 +7378,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7475,12 +7475,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7490,22 +7490,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7587,7 +7587,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7699,7 +7699,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7707,23 +7707,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -7746,7 +7754,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7776,7 +7784,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7786,7 +7794,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7803,12 +7811,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7818,47 +7826,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7888,7 +7896,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7898,7 +7906,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7915,62 +7923,54 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8027,12 +8027,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8042,39 +8042,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8139,12 +8139,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8169,24 +8169,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8251,7 +8251,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8266,22 +8266,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8363,7 +8363,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8378,39 +8378,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8475,7 +8475,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8490,22 +8490,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8587,31 +8587,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8664,7 +8672,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8674,7 +8682,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8691,31 +8699,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8738,7 +8754,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8768,7 +8784,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8778,7 +8794,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8795,7 +8811,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8806,17 +8822,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8842,7 +8858,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8872,7 +8888,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8882,7 +8898,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8899,28 +8915,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8946,7 +8962,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8976,7 +8992,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8986,7 +9002,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9003,7 +9019,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9014,17 +9030,17 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9050,7 +9066,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9080,7 +9096,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9090,7 +9106,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9107,7 +9123,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9115,31 +9131,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9162,7 +9170,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9192,7 +9200,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9202,7 +9210,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9219,7 +9227,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9230,17 +9238,17 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9266,7 +9274,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9296,7 +9304,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9306,7 +9314,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9323,7 +9331,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9338,39 +9346,39 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -9378,7 +9386,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9408,7 +9416,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9418,7 +9426,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9435,39 +9443,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9547,23 +9547,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9571,7 +9575,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9594,7 +9602,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9624,7 +9632,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9634,7 +9642,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9651,12 +9659,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9666,39 +9674,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -9706,7 +9714,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9736,7 +9744,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9746,7 +9754,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9763,39 +9771,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Aberdeen +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9875,12 +9875,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9890,22 +9890,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9987,36 +9987,44 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -10034,7 +10042,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10064,7 +10072,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10074,7 +10082,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10091,12 +10099,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10106,52 +10114,52 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10176,17 +10184,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10203,28 +10211,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10250,7 +10258,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10280,7 +10288,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10290,7 +10298,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10307,31 +10315,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10339,27 +10355,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -10384,17 +10400,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10411,7 +10427,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10422,17 +10438,17 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10443,27 +10459,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10488,17 +10504,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10515,23 +10531,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10592,7 +10608,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10602,7 +10618,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10619,7 +10635,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10630,17 +10646,17 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -10666,7 +10682,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10696,7 +10712,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10706,7 +10722,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10723,7 +10739,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10734,12 +10750,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10800,7 +10816,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10810,7 +10826,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10827,7 +10843,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10904,7 +10920,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10931,39 +10947,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10986,7 +10994,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11016,7 +11024,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11026,7 +11034,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11043,39 +11051,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11155,31 +11155,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11202,7 +11210,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11232,7 +11240,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11242,7 +11250,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11259,7 +11267,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11274,22 +11282,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11314,7 +11322,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11344,7 +11352,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11354,7 +11362,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11371,110 +11379,326 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.3887</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1785526560</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>51.909968</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
+      <c r="V105" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V149"/>
+  <dimension ref="A1:V150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8ceb2c7debb34b8a40b7315d304afa7ee4a54bba21a367911f05e46848128e19</t>
+          <t>0x72f9409f8a47241995267b94c18bbf751e55c0226742848c9189df104101e4f1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>329.4161</t>
+          <t>97.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8538</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Motherwell vs Falkirk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xc8bb30305a2bdf54bf4f0b38e9c8b4eb5f66ba6ed51b2fabaa2d1b0574b60eed</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19673933</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785783654</t>
+          <t>1786027161</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1786284000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>385.846091</t>
+          <t>201.298969</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbb86490b33b6c7545f0bcf6ef6e83bf3a1d9f569231657634f53dd062987cb89</t>
+          <t>0x8ceb2c7debb34b8a40b7315d304afa7ee4a54bba21a367911f05e46848128e19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>228.13362</t>
+          <t>329.4161</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785783652</t>
+          <t>1785783654</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>267.213611</t>
+          <t>385.846091</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x68b90fe04c6d415cfa56fcd9c625a04b992f6838538b94cbb52216d78cfcad94</t>
+          <t>0xbb86490b33b6c7545f0bcf6ef6e83bf3a1d9f569231657634f53dd062987cb89</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,7 +750,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.68046</t>
+          <t>228.13362</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785783646</t>
+          <t>1785783652</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48.820451</t>
+          <t>267.213611</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,54 +843,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x571ee6b748c35d7c669f118e252a764947d201d4cfcc75e171141b0a792b613a</t>
+          <t>0x68b90fe04c6d415cfa56fcd9c625a04b992f6838538b94cbb52216d78cfcad94</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60.01997</t>
+          <t>41.68046</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.8538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Dundee FC</t>
@@ -898,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -938,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>75.61571</t>
+          <t>48.820451</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +947,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x14821b80988157f71abde423baa093a3dc8e81dcc0675b7cff42a2555f49a106</t>
+          <t>0x571ee6b748c35d7c669f118e252a764947d201d4cfcc75e171141b0a792b613a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,22 +962,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.24997</t>
+          <t>60.01997</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8075</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1010,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf188ab0b1af499fdf293e7c4b4e73850b64570a16da4d16265b8b82525ebc8bd</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785783329</t>
+          <t>1785783646</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.54795</t>
+          <t>75.61571</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x3a0d50c20402bfdf793a2ae22ff5413f33d512bac754d7b96b2f8f769a35515e</t>
+          <t>0x14821b80988157f71abde423baa093a3dc8e81dcc0675b7cff42a2555f49a106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1075,23 +1067,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>234.40998</t>
+          <t>1.24997</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.8075</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0xf188ab0b1af499fdf293e7c4b4e73850b64570a16da4d16265b8b82525ebc8bd</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785783126</t>
+          <t>1785783329</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>267.89712</t>
+          <t>1.54795</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6e44f80f198305bfa69cb2046df2d12b0b81220a746685a9bc1c529bbc5f451c</t>
+          <t>0x3a0d50c20402bfdf793a2ae22ff5413f33d512bac754d7b96b2f8f769a35515e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,31 +1179,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>234.40998</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Celtic -2</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1226,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785783112</t>
+          <t>1785783126</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>267.89712</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x66c39787192204a744a96db56c2a69b84e4ec0f2110e397f482646e3367934c9</t>
+          <t>0x6e44f80f198305bfa69cb2046df2d12b0b81220a746685a9bc1c529bbc5f451c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,23 +1283,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>130.21996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8762</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785783066</t>
+          <t>1785783112</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>148.610511</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,28 +1387,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x58b900dc7719a864246dacb3bf3ac5f0571c08a9801cae8440607ad155b6c2b2</t>
+          <t>0x66c39787192204a744a96db56c2a69b84e4ec0f2110e397f482646e3367934c9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350.36886</t>
+          <t>130.21996</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.8762</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785783062</t>
+          <t>1785783066</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>452.088852</t>
+          <t>148.610511</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,39 +1491,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x5615486eb3c0bb7cb2c9cd2a2a6c178f4e7cbc3e532bde7763baabe45deebbea</t>
+          <t>0x58b900dc7719a864246dacb3bf3ac5f0571c08a9801cae8440607ad155b6c2b2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xB978f8e241667aBAc6633e7c71A6785Cfc6Bb85e</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>350.36886</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1546,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1576,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785782552</t>
+          <t>1785783062</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8.333333</t>
+          <t>452.088852</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,31 +1595,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x3b6b6b65c73e2e8c7d0bf83144ff4c108c34a7d820668f1e3c6ea52b41f547c2</t>
+          <t>0x5615486eb3c0bb7cb2c9cd2a2a6c178f4e7cbc3e532bde7763baabe45deebbea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xB978f8e241667aBAc6633e7c71A6785Cfc6Bb85e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785782247</t>
+          <t>1785782552</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.092527</t>
+          <t>8.333333</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,28 +1707,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf297d01d257a461b420e3fea8318fa0cdfc3871b6cbc2a3fa85227e38d0e2485</t>
+          <t>0x3b6b6b65c73e2e8c7d0bf83144ff4c108c34a7d820668f1e3c6ea52b41f547c2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>67.12492</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785781995</t>
+          <t>1785782247</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>98.89491</t>
+          <t>6.092527</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,28 +1811,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x9cfeddb61a7998ff326ffd4ef53a911bda54bd6e1f46069f5f010ea7ed9bcb1e</t>
+          <t>0xf297d01d257a461b420e3fea8318fa0cdfc3871b6cbc2a3fa85227e38d0e2485</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>67.12492</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.1475</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785781981</t>
+          <t>1785781995</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>75.661017</t>
+          <t>98.89491</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x47abb3cd04ee7a423dd6189454a2ce6ece83c4f913dfb5e3ac1904d448d4d6e4</t>
+          <t>0x9cfeddb61a7998ff326ffd4ef53a911bda54bd6e1f46069f5f010ea7ed9bcb1e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>720.745763</t>
+          <t>75.661017</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xe5bc2564623f0b012c2f16062659d5d2db41722f141faa32044ff003cf4f57a5</t>
+          <t>0x47abb3cd04ee7a423dd6189454a2ce6ece83c4f913dfb5e3ac1904d448d4d6e4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2030,17 +2030,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>106.31</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.1475</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785781967</t>
+          <t>1785781981</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>66.814815</t>
+          <t>720.745763</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x143eeddcb2cf0bf76c9f34aae5ed48ebf11c38884a452192df17a441ff862444</t>
+          <t>0xe5bc2564623f0b012c2f16062659d5d2db41722f141faa32044ff003cf4f57a5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2134,17 +2134,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1462</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785781951</t>
+          <t>1785781967</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>181.74359</t>
+          <t>66.814815</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb73b8ca7963b366bc596ffe9222e813eca1d43d84bbbf6fce05eaf4b7151f3a8</t>
+          <t>0x143eeddcb2cf0bf76c9f34aae5ed48ebf11c38884a452192df17a441ff862444</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2238,7 +2238,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785781950</t>
+          <t>1785781951</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>28.17094</t>
+          <t>181.74359</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x408f8039d1304b35c934e1cb0c4fbee2fab249a8ef0973517daa3c23f9c76ac7</t>
+          <t>0xb73b8ca7963b366bc596ffe9222e813eca1d43d84bbbf6fce05eaf4b7151f3a8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2342,7 +2342,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785781921</t>
+          <t>1785781950</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>617.641026</t>
+          <t>28.17094</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x113a31754a4c639b60571df17cd2319c2f97933a295cd6e7cf5af84011d2bc66</t>
+          <t>0x408f8039d1304b35c934e1cb0c4fbee2fab249a8ef0973517daa3c23f9c76ac7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2446,12 +2446,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>1.1462</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785781890</t>
+          <t>1785781921</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>26.827586</t>
+          <t>617.641026</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,23 +2539,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x990455e59b95c1e015471706d5561f3463ff0493d865a6a776f3fc98483367c7</t>
+          <t>0x113a31754a4c639b60571df17cd2319c2f97933a295cd6e7cf5af84011d2bc66</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x883A9941A2a91b39b47EfbA5C4e181e039ab33d5</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.145</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785780502</t>
+          <t>1785781890</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3174.603175</t>
+          <t>26.827586</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,28 +2643,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x437ee08a8ab8fad898ea6e32d81d5c54c11045cbfe8754236794f73898a469d2</t>
+          <t>0x990455e59b95c1e015471706d5561f3463ff0493d865a6a776f3fc98483367c7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x883A9941A2a91b39b47EfbA5C4e181e039ab33d5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.70837</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785780367</t>
+          <t>1785780502</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>40.768387</t>
+          <t>3174.603175</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x56bd58b405f032eb73a48eec1b680b9c1e07be7a72c310441f844f6cbd9ec65a</t>
+          <t>0x437ee08a8ab8fad898ea6e32d81d5c54c11045cbfe8754236794f73898a469d2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2755,31 +2755,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>13.70837</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2802,7 +2794,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2832,7 +2824,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785779934</t>
+          <t>1785780367</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2834,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.195122</t>
+          <t>40.768387</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,12 +2851,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf7aa76476660fdfc5dc70f32e00e85dbaf43eb8b891cd4c45d87e08d1fc026f6</t>
+          <t>0x56bd58b405f032eb73a48eec1b680b9c1e07be7a72c310441f844f6cbd9ec65a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2874,22 +2866,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Over 5.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2914,7 +2906,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2944,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785779463</t>
+          <t>1785779934</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2954,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>41.766004</t>
+          <t>48.195122</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,12 +2963,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x055fd3698fe544232ab7bb2f3242c5943ee368b16f524a7be0ef0ebf1e448449</t>
+          <t>0xf7aa76476660fdfc5dc70f32e00e85dbaf43eb8b891cd4c45d87e08d1fc026f6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3056,7 +3048,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785779252</t>
+          <t>1785779463</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3058,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>8.830022</t>
+          <t>41.766004</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,12 +3075,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xfad1221a399e4d655a299a777ac29b590f421dccc8a9eb5dedae6a07bd922e32</t>
+          <t>0x055fd3698fe544232ab7bb2f3242c5943ee368b16f524a7be0ef0ebf1e448449</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3098,7 +3090,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>56.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3168,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785779218</t>
+          <t>1785779252</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>100.503311</t>
+          <t>8.830022</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,12 +3187,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x12a4f81a80bb8301d63fbdea5443a00d9834f9a29093ed2f6f1114617fcb3858</t>
+          <t>0xfad1221a399e4d655a299a777ac29b590f421dccc8a9eb5dedae6a07bd922e32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3210,7 +3202,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>56.91</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3280,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785779217</t>
+          <t>1785779218</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>8.830022</t>
+          <t>100.503311</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,12 +3299,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfe092458be83504e88fcd874d186ccab65a32366b6ba25b3cf9c01ea5e156323</t>
+          <t>0x12a4f81a80bb8301d63fbdea5443a00d9834f9a29093ed2f6f1114617fcb3858</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3322,7 +3314,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3392,7 +3384,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785779211</t>
+          <t>1785779217</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>56.370861</t>
+          <t>8.830022</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,12 +3411,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xe809f445cf78b6d3c3e7a9ddf02a4c3a3420ce3f3fc06f772107486ebf0e7ed8</t>
+          <t>0xfe092458be83504e88fcd874d186ccab65a32366b6ba25b3cf9c01ea5e156323</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3434,39 +3426,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>149.99995</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>Celtic</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Dundee FC</t>
@@ -3474,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3504,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785779124</t>
+          <t>1785779211</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>174.672431</t>
+          <t>56.370861</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,12 +3523,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x05ead18f604a6fc8acfc65940da77434e156845007987f93819713855b96fc07</t>
+          <t>0xe809f445cf78b6d3c3e7a9ddf02a4c3a3420ce3f3fc06f772107486ebf0e7ed8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3546,22 +3538,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>149.99995</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3586,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785779064</t>
+          <t>1785779124</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>14.233996</t>
+          <t>174.672431</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,12 +3635,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x86e45a2623cd19046dc762c4b8526a81a6660c1e79ec895f1e7583bb6d952eb7</t>
+          <t>0x05ead18f604a6fc8acfc65940da77434e156845007987f93819713855b96fc07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3658,47 +3650,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0462</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3728,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785778383</t>
+          <t>1785779064</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>108.108108</t>
+          <t>14.233996</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,12 +3747,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x8b783ca197d17707cf9a523540713e90da71f36baff8ae33cd09abc4e5c84614</t>
+          <t>0x86e45a2623cd19046dc762c4b8526a81a6660c1e79ec895f1e7583bb6d952eb7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3840,7 +3832,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785778381</t>
+          <t>1785778383</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3867,12 +3859,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1ee84d4d338111f7e4ab7ca72105f131cdaa3fdfd44097321fb17432c6b700be</t>
+          <t>0x8b783ca197d17707cf9a523540713e90da71f36baff8ae33cd09abc4e5c84614</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3882,7 +3874,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3952,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785778348</t>
+          <t>1785778381</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3954,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>379.675676</t>
+          <t>108.108108</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,12 +3971,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2a1a61066e76af75aaa51c94a8e570c93d9d1c3396aa97cf2068401827cf072f</t>
+          <t>0x1ee84d4d338111f7e4ab7ca72105f131cdaa3fdfd44097321fb17432c6b700be</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3994,22 +3986,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.86999</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.0462</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4034,7 +4026,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf549fdea561c409a6de0d63bcaf4bb26625a2c2742145c637791b5ee0fa2a9df</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4064,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785778248</t>
+          <t>1785778348</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4074,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>8.877112</t>
+          <t>379.675676</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,7 +4083,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x020180a33aaa7296e75e3cc3d96ab9e005b79b35aa071cb8c7177fa97cce3f49</t>
+          <t>0x2a1a61066e76af75aaa51c94a8e570c93d9d1c3396aa97cf2068401827cf072f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4106,22 +4098,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>5.86999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4146,7 +4138,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
+          <t>0xf549fdea561c409a6de0d63bcaf4bb26625a2c2742145c637791b5ee0fa2a9df</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4186,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.195122</t>
+          <t>8.877112</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc8208a1ff2e7720a445c58f959ebfce44d19134fc533f041006d7861e367fffc</t>
+          <t>0x020180a33aaa7296e75e3cc3d96ab9e005b79b35aa071cb8c7177fa97cce3f49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4218,22 +4210,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.72999</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Over 5.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4258,7 +4250,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4288,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785778095</t>
+          <t>1785778248</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4.768541</t>
+          <t>48.195122</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,12 +4307,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xa0b7da7907eb8f3c6666bf54d95311b570699677209955c731318ac90d5b12cc</t>
+          <t>0xc8208a1ff2e7720a445c58f959ebfce44d19134fc533f041006d7861e367fffc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4330,22 +4322,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.72999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>1.5725</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Celtic -2</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4400,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785774746</t>
+          <t>1785778095</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4410,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>34.782609</t>
+          <t>4.768541</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4427,12 +4419,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x773a06dbc999f888ebd236897533f8917b81e5e30f878c5f9cbf0b506891f38f</t>
+          <t>0xa0b7da7907eb8f3c6666bf54d95311b570699677209955c731318ac90d5b12cc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4442,22 +4434,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>260.95891</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.115</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Celtic -1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4512,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785772242</t>
+          <t>1785774746</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4522,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>410.958913</t>
+          <t>34.782609</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,12 +4531,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x30bedd8e12f218352b63ed67c5a374e71383d9111f8d1d477c95e73ad9ea88d6</t>
+          <t>0x773a06dbc999f888ebd236897533f8917b81e5e30f878c5f9cbf0b506891f38f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4554,22 +4546,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>69.91</t>
+          <t>260.95891</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Celtic -2.5</t>
+          <t>Celtic -1.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4594,7 +4586,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x1d2532630d73af57585b447d8384d3947217611afe7120da0b6d5050faa03c7c</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4624,7 +4616,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785771847</t>
+          <t>1785772242</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4634,7 +4626,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>167.951952</t>
+          <t>410.958913</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,12 +4643,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x80ff59b0a07ba4733309bfc0fd9cb3bcf96ccad7a81d5f697f3b906a3ffc3ee6</t>
+          <t>0x30bedd8e12f218352b63ed67c5a374e71383d9111f8d1d477c95e73ad9ea88d6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4666,7 +4658,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>69.91</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4736,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785771708</t>
+          <t>1785771847</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4746,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12.012012</t>
+          <t>167.951952</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4763,12 +4755,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x801f71692e83b8cd7d0941462fd3ba6b0a9aaf29b3f7b063a01a4f945602f725</t>
+          <t>0x80ff59b0a07ba4733309bfc0fd9cb3bcf96ccad7a81d5f697f3b906a3ffc3ee6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4778,7 +4770,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4848,7 +4840,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785771676</t>
+          <t>1785771708</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4858,7 +4850,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>34.138138</t>
+          <t>12.012012</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4875,12 +4867,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x11b8c6dfdef5643131a6e77adc415fb0dc20ac1b95816301d7b97fdcc9afd0cc</t>
+          <t>0x801f71692e83b8cd7d0941462fd3ba6b0a9aaf29b3f7b063a01a4f945602f725</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4890,7 +4882,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4960,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785771576</t>
+          <t>1785771676</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4970,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>12.012012</t>
+          <t>34.138138</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4987,7 +4979,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xaed4ca51df24fdd5ec3dec774b15886cf3138e86f1f6dc274a8dfeb4db4dc097</t>
+          <t>0x11b8c6dfdef5643131a6e77adc415fb0dc20ac1b95816301d7b97fdcc9afd0cc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,7 +5064,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785771574</t>
+          <t>1785771576</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5099,12 +5091,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x6cfa56cc3467b80cbe7fd1604fae43c9247f52ff545970ba917a6d8f9bacd48f</t>
+          <t>0xaed4ca51df24fdd5ec3dec774b15886cf3138e86f1f6dc274a8dfeb4db4dc097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5114,7 +5106,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5184,7 +5176,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785771563</t>
+          <t>1785771574</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5194,7 +5186,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>48.072072</t>
+          <t>12.012012</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5211,7 +5203,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x7ed9ca8c1bc7e7194108ab2c066aad81553c4e8bcf5f7b4a9371658d523d01d8</t>
+          <t>0x6cfa56cc3467b80cbe7fd1604fae43c9247f52ff545970ba917a6d8f9bacd48f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5226,7 +5218,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5296,7 +5288,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785771550</t>
+          <t>1785771563</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5306,7 +5298,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>56.408408</t>
+          <t>48.072072</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5323,12 +5315,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xb72a00c5e8da6d7e2b4252e503b7c2bfc4d447755058015c026369de2fbb14f4</t>
+          <t>0x7ed9ca8c1bc7e7194108ab2c066aad81553c4e8bcf5f7b4a9371658d523d01d8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5338,47 +5330,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>178.59</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Celtic -2.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x1d2532630d73af57585b447d8384d3947217611afe7120da0b6d5050faa03c7c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5408,7 +5400,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785767238</t>
+          <t>1785771550</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5418,7 +5410,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2857.44</t>
+          <t>56.408408</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5435,7 +5427,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x9225eefdc660d0c6bcf7f3eda3ca158d40cc8783d07cf561c29062114d1343f4</t>
+          <t>0xb72a00c5e8da6d7e2b4252e503b7c2bfc4d447755058015c026369de2fbb14f4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5450,7 +5442,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>158.45</t>
+          <t>178.59</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5520,7 +5512,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785767197</t>
+          <t>1785767238</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5530,7 +5522,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2535.2</t>
+          <t>2857.44</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5547,12 +5539,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
+          <t>0x9225eefdc660d0c6bcf7f3eda3ca158d40cc8783d07cf561c29062114d1343f4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5562,12 +5554,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>158.45</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5577,7 +5569,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5602,7 +5594,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5632,7 +5624,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785747031</t>
+          <t>1785767197</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5642,7 +5634,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>33.684211</t>
+          <t>2535.2</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5659,12 +5651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
+          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5674,22 +5666,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5714,7 +5706,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5744,7 +5736,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785735473</t>
+          <t>1785747031</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5754,7 +5746,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>9.54652</t>
+          <t>33.684211</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5771,31 +5763,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
+          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>213.04999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
+          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785734664</t>
+          <t>1785735473</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>353.609942</t>
+          <t>9.54652</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5875,28 +5875,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
+          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>213.04999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
+          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785734506</t>
+          <t>1785734664</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13.029412</t>
+          <t>353.609942</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5979,62 +5979,54 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
+          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.5311</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0675</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6064,7 +6056,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785727225</t>
+          <t>1785734506</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6074,7 +6066,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>289.34963</t>
+          <t>13.029412</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6091,23 +6083,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
+          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>19.5311</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0675</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6115,7 +6111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6123,27 +6123,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785682854</t>
+          <t>1785727225</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>289.34963</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6206,7 +6206,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785682817</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6307,19 +6307,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6327,26 +6323,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -6384,7 +6376,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785682785</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6394,7 +6386,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>31.635443</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6411,23 +6403,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>93.10524</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6435,7 +6431,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785682784</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>122.105233</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6526,12 +6526,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>98.4284</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785682781</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>129.298391</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6619,18 +6619,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785682739</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>6.568131</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6723,18 +6723,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19.4816</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785682735</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>25.591593</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6827,18 +6827,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4.60848</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785682733</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>6.053833</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,18 +6931,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>92.46597</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785681750</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>121.46597</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7035,28 +7035,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>32.47659</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (6.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7067,27 +7067,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7112,17 +7112,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785681479</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>61.276585</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7139,28 +7139,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7171,27 +7171,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785680616</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>47.446301</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7243,28 +7243,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>139.68586</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>409.335853</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,7 +7347,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7358,17 +7358,17 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>122.41894</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>233.178933</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,23 +7451,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785680318</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1.34002</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7566,12 +7566,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>168.68</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785680305</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>228.331641</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7670,12 +7670,12 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785678530</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>27.667233</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7763,7 +7763,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7774,7 +7774,7 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>46.31885</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785678083</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>62.911851</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,7 +7867,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7878,12 +7878,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>40.66999</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785677996</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>55.33332</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7982,7 +7982,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12.42999</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785677920</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>16.911551</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8086,7 +8086,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.12999</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785677881</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1.537401</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8179,7 +8179,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8187,19 +8187,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8207,11 +8203,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8234,7 +8226,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8264,7 +8256,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785677338</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8266,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>39.154185</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,12 +8283,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8306,22 +8298,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>55.11998</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8346,7 +8338,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8376,7 +8368,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785677298</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8386,7 +8378,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>73.86262</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8403,12 +8395,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8418,22 +8410,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8458,7 +8450,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8488,7 +8480,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785675836</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8498,7 +8490,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>4.546256</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8515,7 +8507,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8530,7 +8522,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8600,7 +8592,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785675803</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8610,7 +8602,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>9.057269</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8627,7 +8619,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8642,7 +8634,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8712,7 +8704,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8722,7 +8714,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>3.524229</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8739,7 +8731,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8747,15 +8739,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8763,7 +8759,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>3.757303</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8843,7 +8843,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8851,19 +8851,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8871,11 +8867,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8898,7 +8890,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8928,7 +8920,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785672902</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8938,7 +8930,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>59.806167</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8955,7 +8947,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8970,22 +8962,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8995,27 +8987,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9040,17 +9032,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785672780</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>20.675676</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9067,31 +9059,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9099,27 +9099,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9144,17 +9144,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785672554</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9171,23 +9171,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>29.66982</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785672525</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>53.57981</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9275,27 +9275,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9303,11 +9299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9315,27 +9307,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9360,17 +9352,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9387,7 +9379,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9472,7 +9464,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9499,12 +9491,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9514,12 +9506,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9584,7 +9576,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9594,7 +9586,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9611,7 +9603,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9626,12 +9618,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9706,7 +9698,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9723,23 +9715,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9747,7 +9743,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9755,27 +9755,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9800,17 +9800,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9827,7 +9827,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9835,19 +9835,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9855,26 +9851,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -9882,7 +9874,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9912,7 +9904,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9922,7 +9914,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9939,7 +9931,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9947,15 +9939,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9963,7 +9959,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10043,7 +10043,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10147,7 +10147,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10158,12 +10158,12 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10251,7 +10251,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10262,12 +10262,12 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10355,7 +10355,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10366,7 +10366,7 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,7 +10459,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10470,12 +10470,12 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,7 +10563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10574,12 +10574,12 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10678,12 +10678,12 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10771,7 +10771,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10886,12 +10886,12 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10990,12 +10990,12 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11083,7 +11083,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11094,7 +11094,7 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11187,27 +11187,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11215,26 +11211,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -11242,7 +11234,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11272,7 +11264,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11282,7 +11274,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11299,23 +11291,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11323,7 +11319,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11331,27 +11331,27 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11403,27 +11403,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11431,11 +11427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11443,27 +11435,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -11488,17 +11480,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11515,59 +11507,67 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -11592,17 +11592,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11619,7 +11619,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11630,7 +11630,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11723,7 +11723,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11734,17 +11734,17 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11835,31 +11835,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11867,27 +11859,27 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -11912,17 +11904,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11939,7 +11931,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11954,12 +11946,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -12024,7 +12016,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -12034,7 +12026,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12051,7 +12043,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12059,23 +12051,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12083,27 +12083,27 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -12128,17 +12128,17 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12155,39 +12155,31 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12195,27 +12187,27 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -12240,17 +12232,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12267,12 +12259,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12282,22 +12274,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12322,7 +12314,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -12352,7 +12344,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -12362,7 +12354,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12379,12 +12371,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12394,39 +12386,39 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -12434,7 +12426,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12464,7 +12456,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12474,7 +12466,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12491,7 +12483,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12506,22 +12498,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12546,7 +12538,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12576,7 +12568,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12586,7 +12578,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12603,7 +12595,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12618,39 +12610,39 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -12658,7 +12650,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -12688,7 +12680,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12698,7 +12690,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12715,7 +12707,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12723,23 +12715,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12819,62 +12819,54 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -12904,7 +12896,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12914,7 +12906,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -12931,12 +12923,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12946,7 +12938,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13016,7 +13008,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -13026,7 +13018,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13043,12 +13035,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13058,39 +13050,39 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K118" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -13098,7 +13090,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13128,7 +13120,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -13138,7 +13130,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13155,7 +13147,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13170,17 +13162,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -13210,7 +13202,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -13240,7 +13232,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -13250,7 +13242,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13267,7 +13259,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13282,22 +13274,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13322,7 +13314,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -13352,7 +13344,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1785604008</t>
+          <t>1785604011</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -13362,7 +13354,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>1533.879181</t>
+          <t>549.929412</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13379,7 +13371,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
+          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13394,39 +13386,39 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>1142.73999</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -13434,7 +13426,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -13464,7 +13456,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>1785604004</t>
+          <t>1785604008</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -13474,7 +13466,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>570.738739</t>
+          <t>1533.879181</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -13491,7 +13483,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
+          <t>0xee92ca9c29ea82990989cd8f4f18a9271dfaee1ee58ee39ff9d4ea8cae6162fa</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13506,22 +13498,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>238.03781</t>
+          <t>79.19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13546,7 +13538,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -13586,7 +13578,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>729.617808</t>
+          <t>570.738739</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -13603,31 +13595,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
+          <t>0x481f2136c4218797be6f5498911a758cd98b7d2b25a64fc22ad7599ea294c18f</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>238.03781</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0xc827c4361285ff3730f2a2827cfaf4c676a98131c5260897f68817741137c35d</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>1785603521</t>
+          <t>1785604004</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>538.699088</t>
+          <t>729.617808</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -13707,28 +13707,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
+          <t>0xf1ff5187b59c2c170177f0b5168e643e683b6267c1d47d6354dd0c2cd7e3db7f</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>221.54</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>1785603172</t>
+          <t>1785603521</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>77.902913</t>
+          <t>538.699088</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -13811,23 +13811,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
+          <t>0x7038e38303a9c1caaff6ad103dd90e763a7ed2daf0187c1c30eaf28493a7c535</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>1785602480</t>
+          <t>1785603172</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>46.355828</t>
+          <t>77.902913</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -13915,7 +13915,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
+          <t>0x5593ee9dbf8234ebc5cd2d7f63a0cab2a7089790a5725d69d2bea597242e072a</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13926,17 +13926,17 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>1785602424</t>
+          <t>1785602480</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>11.482759</t>
+          <t>46.355828</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14019,7 +14019,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
+          <t>0xdeb734fd55693d6bb57dd13b4a021a04041a2a7e576b65b08d43832ab4f5a527</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -14030,17 +14030,17 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0x9a443e546e77e9f80d33b52f010c5e5cb8a79df43a9ca840a543143b3d478ef4</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>1785600627</t>
+          <t>1785602424</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>14.092715</t>
+          <t>11.482759</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14123,7 +14123,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
+          <t>0xfb04bbcdc9241892746a7738b4d43299feeb4ae5ea1ac018cc8b4cf8c1ce3ed8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -14131,31 +14131,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -14178,7 +14170,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -14218,7 +14210,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>48.537549</t>
+          <t>14.092715</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -14235,7 +14227,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
+          <t>0xd634bf9e90e95d19255887ff5a09adbbd49f87a461799c010aea102c31335d65</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14243,23 +14235,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>1785600583</t>
+          <t>1785600627</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>16.73029</t>
+          <t>48.537549</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14339,7 +14339,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
+          <t>0x9928666cf9e1684bde5a3ebbe01a541c8265a2a2941c672ef774c0600b8a312d</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -14347,19 +14347,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14367,26 +14363,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -14394,7 +14386,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -14424,7 +14416,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>1785600448</t>
+          <t>1785600583</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -14434,7 +14426,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>30.651341</t>
+          <t>16.73029</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14451,12 +14443,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
+          <t>0xb5bac00ce7791648a87a47dcb5171aa144f49ab021c1a0dfad750f804d93836a</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14466,22 +14458,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1.3162</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -14506,7 +14498,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -14536,7 +14528,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>1785600138</t>
+          <t>1785600448</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -14546,7 +14538,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>22.513834</t>
+          <t>30.651341</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -14563,7 +14555,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
+          <t>0x38706f9171542d01bce83eea0f508d61220ed3812837fd3378a4ba9378ad3044</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -14571,23 +14563,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>622.70999</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.3162</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x04e9c93b2a3cdb04295c6e42b353a7f36caf0911c8f1d076ed9845d827b65319</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1785599983</t>
+          <t>1785600138</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>1044.377342</t>
+          <t>22.513834</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -14667,27 +14667,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
+          <t>0x0abfa4d97fa8b65021131d51b5e7a11807375335069de4074a6958eb5933bf1b</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>622.70999</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1.3275</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14695,26 +14691,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -14722,7 +14714,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -14752,7 +14744,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>1785598284</t>
+          <t>1785599983</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -14762,7 +14754,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>3.053435</t>
+          <t>1044.377342</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -14779,12 +14771,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
+          <t>0xf58dccabb95967ececb3018f2817565106376fd483b468b19405c12cb8a59ef0</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14794,22 +14786,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>37.20755</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.3275</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Aberdeen +0.5</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -14834,7 +14826,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -14864,7 +14856,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>1785598183</t>
+          <t>1785598284</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -14874,7 +14866,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>62.797553</t>
+          <t>3.053435</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -14891,7 +14883,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
+          <t>0x9f0d5bbd68c46acf848124b165bc9e44a297569da9b235fd670f59e4806967f4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -14906,7 +14898,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>253.59</t>
+          <t>37.20755</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -14976,7 +14968,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>1785598181</t>
+          <t>1785598183</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -14986,7 +14978,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>62.797553</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -15003,36 +14995,44 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
+          <t>0x32207acd736daa9a5552c759f251892aae7c67eae4995d245e53e2ae553b5041</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>253.59</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Aberdeen +0.5</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>Aberdeen vs Heart of Midlothian</t>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
+          <t>0xe279716d54dc617cd67bb4cb03a250c91fe3454ebf59dbcdeff34fb6943400c4</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>1785597811</t>
+          <t>1785598181</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>48.165517</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -15107,27 +15107,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
+          <t>0xf8991a6d899a35a1bbf1d6b29c0560594141a4c87048ff44daa3a7919d9b8b20</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>118.87998</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15135,11 +15131,7 @@
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -15147,27 +15139,27 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
+          <t>0xdea6c0813852afb4b4bf13cca885f2c863ecc81b5b718a5c2a162a3f0f1bb308</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -15192,17 +15184,17 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>1785597330</t>
+          <t>1785597811</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>129.56946</t>
+          <t>48.165517</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -15219,31 +15211,39 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
+          <t>0xa84f14f5567e2b0ab922888be149003601a2966dcb690de037578a4f11fa4120</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>118.87998</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -15251,27 +15251,27 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x1c5d0942acd8f3112cad4143a69702ae70fc03bc778aa6766837908f97e14fbf</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -15296,17 +15296,17 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>1785543200</t>
+          <t>1785597330</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>1.713062</t>
+          <t>129.56946</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -15323,28 +15323,28 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
+          <t>0xe833e969b88818e2354a4b8957b6d20896a41f4b0c3bb51d8ce17572c37d85b1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>40.29346</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -15355,27 +15355,27 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Dundee United vs Rangers FC</t>
+          <t>Aberdeen vs Heart of Midlothian</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Rangers FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>L19228047</t>
+          <t>L19228039</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -15400,17 +15400,17 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>1785529916</t>
+          <t>1785543200</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>1785524400</t>
+          <t>1785601800</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>90.293468</t>
+          <t>1.713062</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -15427,18 +15427,18 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
+          <t>0x38a2ec9c46673affecf2dd2e40bb35b3ce724ee1abcf2ea7bf46223f3d2dae29</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>40.29346</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>1785529915</t>
+          <t>1785529916</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>2.577031</t>
+          <t>90.293468</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -15531,7 +15531,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
+          <t>0x811525e57f52b3cd51b87498ca835dafe03edd882923f8b295bf84dba438dba9</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>1785529816</t>
+          <t>1785529915</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>2.754491</t>
+          <t>2.577031</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -15635,7 +15635,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
+          <t>0x756c0d9d6c86ffc6c9a574910bef44e4e7a8572808cc31e7a38fe7d763b5bb12</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -15646,17 +15646,17 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1785529105</t>
+          <t>1785529816</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>2.754491</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -15739,7 +15739,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
+          <t>0x9190b7571f2e54f6eeb0960c36b8e7815945cd0272019485a9ed234a596e5e0c</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -15750,17 +15750,17 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1.2612</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>1785529104</t>
+          <t>1785529105</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>6.77512</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -15843,7 +15843,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
+          <t>0x9f8081a9f8d3cf12a4a6ef88f2c8a5b07d8d8deb1bf4e72aeadad4553f251e99</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -15854,17 +15854,17 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
+          <t>0x134066d0292ae65674d11acfc245189b0f5932f143c0a3f1508a373a813e3370</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>1.587302</t>
+          <t>6.77512</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -15947,39 +15947,31 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
+          <t>0x7823d9cbc25df4d2ce923f58fdd31cdf09205f13511bea821d348907cd22f22b</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1.1313</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -16002,7 +15994,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
+          <t>0xf4790f2265dea909876b7e0ddbb9612ac90d7a9e27eb0f3a900718ee6f3d4d8d</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -16032,7 +16024,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>1785526843</t>
+          <t>1785529104</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -16042,7 +16034,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>574.780952</t>
+          <t>1.587302</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -16059,7 +16051,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
+          <t>0x8eab29b3cce3f4590878b635836cd9dfe77938580dd4c4e944609e2f28faee9f</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -16074,22 +16066,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.1313</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -16114,7 +16106,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
+          <t>0x8ce8caee1fc33396cbda0b25dd4e673601e00cb200433d43cbc7ba6557ab6a27</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -16154,7 +16146,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>1061.0625</t>
+          <t>574.780952</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -16171,31 +16163,39 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
+          <t>0x75093cdd72db1ee3eae26e5ff6b6b750f8c641928612fa8fc050e56e073b27cf</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>169.77</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1.3887</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
+          <t>0xaef8117e7be3102f22003e6f0ba8d793562daea0942b2a11fa4604e29487dabf</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>1785526560</t>
+          <t>1785526843</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>51.909968</t>
+          <t>1061.0625</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -16275,39 +16275,31 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+          <t>0x512f75a4e040002ce3fcaac79c15ee564e7d883b0c6f03de771b74316f733540</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3887</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -16330,7 +16322,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+          <t>0xe1678df7687688d2ba9549ce444adeb9cc47cb904df706528a6fe7b9800dc519</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -16360,7 +16352,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>1785524635</t>
+          <t>1785526560</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -16370,7 +16362,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>659.783784</t>
+          <t>51.909968</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -16387,110 +16379,222 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>0x1c754a278d7506d77f69973cf1876693bd5c2beb11810930bf32075703a0f973</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1.0925</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Dundee United vs Rangers FC</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Rangers FC</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>0x754c07be0249040cb3ac1bfbc49ca63bd34d58e9cfc2ec300ae5eab844f3a05b</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>L19228047</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>1785524635</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>1785524400</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>659.783784</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>0x3a6afc0d74597a50f894e10c8d93084fcb7ca5e09aa24a3eab1b5f521c2b6e08</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>0xCCdf6F3306aa9df4a4852FaF67fA1e1D58c4Db4e</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
         <is>
           <t>176.04</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>1.495</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>Over 3.0</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>Dundee United vs Rangers FC</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>Dundee United</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="K150" t="inlineStr">
         <is>
           <t>Rangers FC</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>0x2af09a7c30a9c2f3a49f480d1eba3b8573b203b8cb5cec998c89bf8da583850a</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>L19228047</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
         <is>
           <t>1785524138</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
+      <c r="S150" t="inlineStr">
         <is>
           <t>1785524400</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="T150" t="inlineStr">
         <is>
           <t>355.636364</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="U150" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
+      <c r="V150" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Premiership/trades.xlsx
+++ b/data/sxbet/ligas/Premiership/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V150"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x72f9409f8a47241995267b94c18bbf751e55c0226742848c9189df104101e4f1</t>
+          <t>0xa3b2ae022b33125a11f4fb1fc258c699704849aaba775f178b9b28d4800af8e3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,15 +539,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.2412</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Falkirk</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc8bb30305a2bdf54bf4f0b38e9c8b4eb5f66ba6ed51b2fabaa2d1b0574b60eed</t>
+          <t>0xcebf15546c8dbb61d6cd27c72971fd8b5848b897e4c17329477e0e6a644d566e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786027161</t>
+          <t>1786040583</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>201.298969</t>
+          <t>28.974093</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8ceb2c7debb34b8a40b7315d304afa7ee4a54bba21a367911f05e46848128e19</t>
+          <t>0x72f9409f8a47241995267b94c18bbf751e55c0226742848c9189df104101e4f1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>329.4161</t>
+          <t>97.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8538</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Celtic vs Dundee FC</t>
+          <t>Motherwell vs Falkirk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dundee FC</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xc8bb30305a2bdf54bf4f0b38e9c8b4eb5f66ba6ed51b2fabaa2d1b0574b60eed</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19228045</t>
+          <t>L19673933</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785783654</t>
+          <t>1786027161</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785781800</t>
+          <t>1786284000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>385.846091</t>
+          <t>201.298969</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbb86490b33b6c7545f0bcf6ef6e83bf3a1d9f569231657634f53dd062987cb89</t>
+          <t>0x8ceb2c7debb34b8a40b7315d304afa7ee4a54bba21a367911f05e46848128e19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,7 +758,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>228.13362</t>
+          <t>329.4161</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785783652</t>
+          <t>1785783654</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>267.213611</t>
+          <t>385.846091</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x68b90fe04c6d415cfa56fcd9c625a04b992f6838538b94cbb52216d78cfcad94</t>
+          <t>0xbb86490b33b6c7545f0bcf6ef6e83bf3a1d9f569231657634f53dd062987cb89</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,7 +862,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.68046</t>
+          <t>228.13362</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785783646</t>
+          <t>1785783652</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.820451</t>
+          <t>267.213611</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,54 +955,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x571ee6b748c35d7c669f118e252a764947d201d4cfcc75e171141b0a792b613a</t>
+          <t>0x68b90fe04c6d415cfa56fcd9c625a04b992f6838538b94cbb52216d78cfcad94</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.01997</t>
+          <t>41.68046</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.8538</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Dundee FC</t>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>75.61571</t>
+          <t>48.820451</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,12 +1059,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x14821b80988157f71abde423baa093a3dc8e81dcc0675b7cff42a2555f49a106</t>
+          <t>0x571ee6b748c35d7c669f118e252a764947d201d4cfcc75e171141b0a792b613a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24997</t>
+          <t>60.01997</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8075</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf188ab0b1af499fdf293e7c4b4e73850b64570a16da4d16265b8b82525ebc8bd</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785783329</t>
+          <t>1785783646</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.54795</t>
+          <t>75.61571</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3a0d50c20402bfdf793a2ae22ff5413f33d512bac754d7b96b2f8f769a35515e</t>
+          <t>0x14821b80988157f71abde423baa093a3dc8e81dcc0675b7cff42a2555f49a106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,23 +1179,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>234.40998</t>
+          <t>1.24997</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.8075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0xf188ab0b1af499fdf293e7c4b4e73850b64570a16da4d16265b8b82525ebc8bd</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785783126</t>
+          <t>1785783329</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>267.89712</t>
+          <t>1.54795</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6e44f80f198305bfa69cb2046df2d12b0b81220a746685a9bc1c529bbc5f451c</t>
+          <t>0x3a0d50c20402bfdf793a2ae22ff5413f33d512bac754d7b96b2f8f769a35515e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1283,31 +1291,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>234.40998</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Celtic -2</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785783112</t>
+          <t>1785783126</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>267.89712</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x66c39787192204a744a96db56c2a69b84e4ec0f2110e397f482646e3367934c9</t>
+          <t>0x6e44f80f198305bfa69cb2046df2d12b0b81220a746685a9bc1c529bbc5f451c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1395,23 +1395,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>130.21996</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.8762</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1434,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785783066</t>
+          <t>1785783112</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>148.610511</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,28 +1499,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x58b900dc7719a864246dacb3bf3ac5f0571c08a9801cae8440607ad155b6c2b2</t>
+          <t>0x66c39787192204a744a96db56c2a69b84e4ec0f2110e397f482646e3367934c9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>350.36886</t>
+          <t>130.21996</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.8762</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1538,7 +1546,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785783062</t>
+          <t>1785783066</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>452.088852</t>
+          <t>148.610511</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,39 +1603,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5615486eb3c0bb7cb2c9cd2a2a6c178f4e7cbc3e532bde7763baabe45deebbea</t>
+          <t>0x58b900dc7719a864246dacb3bf3ac5f0571c08a9801cae8440607ad155b6c2b2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xB978f8e241667aBAc6633e7c71A6785Cfc6Bb85e</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>350.36886</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785782552</t>
+          <t>1785783062</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.333333</t>
+          <t>452.088852</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,31 +1707,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3b6b6b65c73e2e8c7d0bf83144ff4c108c34a7d820668f1e3c6ea52b41f547c2</t>
+          <t>0x5615486eb3c0bb7cb2c9cd2a2a6c178f4e7cbc3e532bde7763baabe45deebbea</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xB978f8e241667aBAc6633e7c71A6785Cfc6Bb85e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -1754,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1784,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785782247</t>
+          <t>1785782552</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6.092527</t>
+          <t>8.333333</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,28 +1819,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xf297d01d257a461b420e3fea8318fa0cdfc3871b6cbc2a3fa85227e38d0e2485</t>
+          <t>0x3b6b6b65c73e2e8c7d0bf83144ff4c108c34a7d820668f1e3c6ea52b41f547c2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>67.12492</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6787</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785781995</t>
+          <t>1785782247</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>98.89491</t>
+          <t>6.092527</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,28 +1923,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x9cfeddb61a7998ff326ffd4ef53a911bda54bd6e1f46069f5f010ea7ed9bcb1e</t>
+          <t>0xf297d01d257a461b420e3fea8318fa0cdfc3871b6cbc2a3fa85227e38d0e2485</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>67.12492</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1475</t>
+          <t>1.6787</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1962,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x52654e628af1b8edd1821f467832f266f1fd905e77ad0c4961374dc2035006f6</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785781981</t>
+          <t>1785781995</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>75.661017</t>
+          <t>98.89491</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x47abb3cd04ee7a423dd6189454a2ce6ece83c4f913dfb5e3ac1904d448d4d6e4</t>
+          <t>0x9cfeddb61a7998ff326ffd4ef53a911bda54bd6e1f46069f5f010ea7ed9bcb1e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2030,7 +2038,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>106.31</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>720.745763</t>
+          <t>75.661017</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe5bc2564623f0b012c2f16062659d5d2db41722f141faa32044ff003cf4f57a5</t>
+          <t>0x47abb3cd04ee7a423dd6189454a2ce6ece83c4f913dfb5e3ac1904d448d4d6e4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2134,17 +2142,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>106.31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3375</t>
+          <t>1.1475</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2170,7 +2178,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785781967</t>
+          <t>1785781981</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>66.814815</t>
+          <t>720.745763</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x143eeddcb2cf0bf76c9f34aae5ed48ebf11c38884a452192df17a441ff862444</t>
+          <t>0xe5bc2564623f0b012c2f16062659d5d2db41722f141faa32044ff003cf4f57a5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2238,17 +2246,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.1462</t>
+          <t>1.3375</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2274,7 +2282,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2304,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785781951</t>
+          <t>1785781967</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>181.74359</t>
+          <t>66.814815</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,7 +2339,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb73b8ca7963b366bc596ffe9222e813eca1d43d84bbbf6fce05eaf4b7151f3a8</t>
+          <t>0x143eeddcb2cf0bf76c9f34aae5ed48ebf11c38884a452192df17a441ff862444</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2342,7 +2350,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2408,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785781950</t>
+          <t>1785781951</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>28.17094</t>
+          <t>181.74359</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,7 +2443,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x408f8039d1304b35c934e1cb0c4fbee2fab249a8ef0973517daa3c23f9c76ac7</t>
+          <t>0xb73b8ca7963b366bc596ffe9222e813eca1d43d84bbbf6fce05eaf4b7151f3a8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2446,7 +2454,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2512,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785781921</t>
+          <t>1785781950</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2522,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>617.641026</t>
+          <t>28.17094</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,7 +2547,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x113a31754a4c639b60571df17cd2319c2f97933a295cd6e7cf5af84011d2bc66</t>
+          <t>0x408f8039d1304b35c934e1cb0c4fbee2fab249a8ef0973517daa3c23f9c76ac7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2550,12 +2558,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>1.1462</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785781890</t>
+          <t>1785781921</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2634,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>26.827586</t>
+          <t>617.641026</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,23 +2651,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x990455e59b95c1e015471706d5561f3463ff0493d865a6a776f3fc98483367c7</t>
+          <t>0x113a31754a4c639b60571df17cd2319c2f97933a295cd6e7cf5af84011d2bc66</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x883A9941A2a91b39b47EfbA5C4e181e039ab33d5</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.145</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2720,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785780502</t>
+          <t>1785781890</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2730,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>3174.603175</t>
+          <t>26.827586</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,28 +2755,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x437ee08a8ab8fad898ea6e32d81d5c54c11045cbfe8754236794f73898a469d2</t>
+          <t>0x990455e59b95c1e015471706d5561f3463ff0493d865a6a776f3fc98483367c7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x883A9941A2a91b39b47EfbA5C4e181e039ab33d5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.70837</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2794,7 +2802,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2824,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785780367</t>
+          <t>1785780502</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>40.768387</t>
+          <t>3174.603175</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,7 +2859,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x56bd58b405f032eb73a48eec1b680b9c1e07be7a72c310441f844f6cbd9ec65a</t>
+          <t>0x437ee08a8ab8fad898ea6e32d81d5c54c11045cbfe8754236794f73898a469d2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2859,31 +2867,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>13.70837</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785779934</t>
+          <t>1785780367</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.195122</t>
+          <t>40.768387</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xf7aa76476660fdfc5dc70f32e00e85dbaf43eb8b891cd4c45d87e08d1fc026f6</t>
+          <t>0x56bd58b405f032eb73a48eec1b680b9c1e07be7a72c310441f844f6cbd9ec65a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Over 5.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785779463</t>
+          <t>1785779934</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>41.766004</t>
+          <t>48.195122</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,12 +3075,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x055fd3698fe544232ab7bb2f3242c5943ee368b16f524a7be0ef0ebf1e448449</t>
+          <t>0xf7aa76476660fdfc5dc70f32e00e85dbaf43eb8b891cd4c45d87e08d1fc026f6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785779252</t>
+          <t>1785779463</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>8.830022</t>
+          <t>41.766004</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xfad1221a399e4d655a299a777ac29b590f421dccc8a9eb5dedae6a07bd922e32</t>
+          <t>0x055fd3698fe544232ab7bb2f3242c5943ee368b16f524a7be0ef0ebf1e448449</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>56.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785779218</t>
+          <t>1785779252</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>100.503311</t>
+          <t>8.830022</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x12a4f81a80bb8301d63fbdea5443a00d9834f9a29093ed2f6f1114617fcb3858</t>
+          <t>0xfad1221a399e4d655a299a777ac29b590f421dccc8a9eb5dedae6a07bd922e32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>56.91</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785779217</t>
+          <t>1785779218</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>8.830022</t>
+          <t>100.503311</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,12 +3411,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xfe092458be83504e88fcd874d186ccab65a32366b6ba25b3cf9c01ea5e156323</t>
+          <t>0x12a4f81a80bb8301d63fbdea5443a00d9834f9a29093ed2f6f1114617fcb3858</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785779211</t>
+          <t>1785779217</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>56.370861</t>
+          <t>8.830022</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,12 +3523,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xe809f445cf78b6d3c3e7a9ddf02a4c3a3420ce3f3fc06f772107486ebf0e7ed8</t>
+          <t>0xfe092458be83504e88fcd874d186ccab65a32366b6ba25b3cf9c01ea5e156323</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3538,39 +3538,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>149.99995</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Celtic</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Dundee FC</t>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785779124</t>
+          <t>1785779211</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>174.672431</t>
+          <t>56.370861</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x05ead18f604a6fc8acfc65940da77434e156845007987f93819713855b96fc07</t>
+          <t>0xe809f445cf78b6d3c3e7a9ddf02a4c3a3420ce3f3fc06f772107486ebf0e7ed8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>149.99995</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0xdf9ff864e2d9f3dfced6e684909937cc350f65c8d33cdd1fcb6d8920fc4f44ef</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785779064</t>
+          <t>1785779124</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14.233996</t>
+          <t>174.672431</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x86e45a2623cd19046dc762c4b8526a81a6660c1e79ec895f1e7583bb6d952eb7</t>
+          <t>0x05ead18f604a6fc8acfc65940da77434e156845007987f93819713855b96fc07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3762,47 +3762,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0462</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Celtic -2</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785778383</t>
+          <t>1785779064</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>108.108108</t>
+          <t>14.233996</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x8b783ca197d17707cf9a523540713e90da71f36baff8ae33cd09abc4e5c84614</t>
+          <t>0x86e45a2623cd19046dc762c4b8526a81a6660c1e79ec895f1e7583bb6d952eb7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785778381</t>
+          <t>1785778383</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3971,12 +3971,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1ee84d4d338111f7e4ab7ca72105f131cdaa3fdfd44097321fb17432c6b700be</t>
+          <t>0x8b783ca197d17707cf9a523540713e90da71f36baff8ae33cd09abc4e5c84614</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785778348</t>
+          <t>1785778381</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>379.675676</t>
+          <t>108.108108</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x2a1a61066e76af75aaa51c94a8e570c93d9d1c3396aa97cf2068401827cf072f</t>
+          <t>0x1ee84d4d338111f7e4ab7ca72105f131cdaa3fdfd44097321fb17432c6b700be</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.86999</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6612</t>
+          <t>1.0462</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xf549fdea561c409a6de0d63bcaf4bb26625a2c2742145c637791b5ee0fa2a9df</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785778248</t>
+          <t>1785778348</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>8.877112</t>
+          <t>379.675676</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x020180a33aaa7296e75e3cc3d96ab9e005b79b35aa071cb8c7177fa97cce3f49</t>
+          <t>0x2a1a61066e76af75aaa51c94a8e570c93d9d1c3396aa97cf2068401827cf072f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,22 +4210,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>5.86999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.6612</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
+          <t>0xf549fdea561c409a6de0d63bcaf4bb26625a2c2742145c637791b5ee0fa2a9df</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>48.195122</t>
+          <t>8.877112</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xc8208a1ff2e7720a445c58f959ebfce44d19134fc533f041006d7861e367fffc</t>
+          <t>0x020180a33aaa7296e75e3cc3d96ab9e005b79b35aa071cb8c7177fa97cce3f49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4322,22 +4322,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.72999</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Celtic -2</t>
+          <t>Over 5.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
+          <t>0x17355ecd9206affbb79bcbdcc5a42329bb038cf94a7fa5fe4a475ab934826c19</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785778095</t>
+          <t>1785778248</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>4.768541</t>
+          <t>48.195122</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa0b7da7907eb8f3c6666bf54d95311b570699677209955c731318ac90d5b12cc</t>
+          <t>0xc8208a1ff2e7720a445c58f959ebfce44d19134fc533f041006d7861e367fffc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.72999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>1.5725</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Celtic -2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x19b58ada6e79741a2f6333f985b72fb00326a75f2d308c7d60fffc2a0db82b1c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785774746</t>
+          <t>1785778095</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>34.782609</t>
+          <t>4.768541</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,12 +4531,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x773a06dbc999f888ebd236897533f8917b81e5e30f878c5f9cbf0b506891f38f</t>
+          <t>0xa0b7da7907eb8f3c6666bf54d95311b570699677209955c731318ac90d5b12cc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4546,22 +4546,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>260.95891</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.115</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Celtic -1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785772242</t>
+          <t>1785774746</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>410.958913</t>
+          <t>34.782609</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,12 +4643,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x30bedd8e12f218352b63ed67c5a374e71383d9111f8d1d477c95e73ad9ea88d6</t>
+          <t>0x773a06dbc999f888ebd236897533f8917b81e5e30f878c5f9cbf0b506891f38f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>69.91</t>
+          <t>260.95891</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Celtic -2.5</t>
+          <t>Celtic -1.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x1d2532630d73af57585b447d8384d3947217611afe7120da0b6d5050faa03c7c</t>
+          <t>0xb2131091467128823ab4c021207ba36f501bb5f94eae868ad75231f12ef67741</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785771847</t>
+          <t>1785772242</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>167.951952</t>
+          <t>410.958913</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,12 +4755,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x80ff59b0a07ba4733309bfc0fd9cb3bcf96ccad7a81d5f697f3b906a3ffc3ee6</t>
+          <t>0x30bedd8e12f218352b63ed67c5a374e71383d9111f8d1d477c95e73ad9ea88d6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>69.91</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785771708</t>
+          <t>1785771847</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12.012012</t>
+          <t>167.951952</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,12 +4867,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x801f71692e83b8cd7d0941462fd3ba6b0a9aaf29b3f7b063a01a4f945602f725</t>
+          <t>0x80ff59b0a07ba4733309bfc0fd9cb3bcf96ccad7a81d5f697f3b906a3ffc3ee6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785771676</t>
+          <t>1785771708</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>34.138138</t>
+          <t>12.012012</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,12 +4979,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x11b8c6dfdef5643131a6e77adc415fb0dc20ac1b95816301d7b97fdcc9afd0cc</t>
+          <t>0x801f71692e83b8cd7d0941462fd3ba6b0a9aaf29b3f7b063a01a4f945602f725</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785771576</t>
+          <t>1785771676</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>12.012012</t>
+          <t>34.138138</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xaed4ca51df24fdd5ec3dec774b15886cf3138e86f1f6dc274a8dfeb4db4dc097</t>
+          <t>0x11b8c6dfdef5643131a6e77adc415fb0dc20ac1b95816301d7b97fdcc9afd0cc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785771574</t>
+          <t>1785771576</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5203,12 +5203,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x6cfa56cc3467b80cbe7fd1604fae43c9247f52ff545970ba917a6d8f9bacd48f</t>
+          <t>0xaed4ca51df24fdd5ec3dec774b15886cf3138e86f1f6dc274a8dfeb4db4dc097</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785771563</t>
+          <t>1785771574</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>48.072072</t>
+          <t>12.012012</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5315,7 +5315,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x7ed9ca8c1bc7e7194108ab2c066aad81553c4e8bcf5f7b4a9371658d523d01d8</t>
+          <t>0x6cfa56cc3467b80cbe7fd1604fae43c9247f52ff545970ba917a6d8f9bacd48f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785771550</t>
+          <t>1785771563</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>56.408408</t>
+          <t>48.072072</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5427,12 +5427,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xb72a00c5e8da6d7e2b4252e503b7c2bfc4d447755058015c026369de2fbb14f4</t>
+          <t>0x7ed9ca8c1bc7e7194108ab2c066aad81553c4e8bcf5f7b4a9371658d523d01d8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5442,47 +5442,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>178.59</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Celtic -2.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x1d2532630d73af57585b447d8384d3947217611afe7120da0b6d5050faa03c7c</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785767238</t>
+          <t>1785771550</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2857.44</t>
+          <t>56.408408</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5539,7 +5539,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x9225eefdc660d0c6bcf7f3eda3ca158d40cc8783d07cf561c29062114d1343f4</t>
+          <t>0xb72a00c5e8da6d7e2b4252e503b7c2bfc4d447755058015c026369de2fbb14f4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>158.45</t>
+          <t>178.59</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785767197</t>
+          <t>1785767238</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2535.2</t>
+          <t>2857.44</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5651,12 +5651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
+          <t>0x9225eefdc660d0c6bcf7f3eda3ca158d40cc8783d07cf561c29062114d1343f4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>158.45</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785747031</t>
+          <t>1785767197</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>33.684211</t>
+          <t>2535.2</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
+          <t>0x49fe4c2648510573c854699789141b589c73f74e64f5df72becb0a6f521cded8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xF19931164a8F0665292B4426D5C5aCAC1CBF8352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5778,22 +5778,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
+          <t>0xca9bc667ecd35f4117229c6bfffcd056315b62043c5aed746d70831e9a17a27c</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785735473</t>
+          <t>1785747031</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>9.54652</t>
+          <t>33.684211</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5875,31 +5875,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
+          <t>0xd8a104c4ba237d7a08ed100d1dc369815313bd94bd759bb1a0904fe6aa8d8d28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>213.04999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6025</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -5922,7 +5930,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
+          <t>0xd54104f97e4279884642e3bdcd066a6f503d28df2502de02dbad34014095fbe9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5952,7 +5960,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785734664</t>
+          <t>1785735473</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5962,7 +5970,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>353.609942</t>
+          <t>9.54652</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5979,28 +5987,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
+          <t>0x35c5319d52a90091e3447bdb067a98f134eb85fcc7843ad4a8be13ea4e8de626</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>213.04999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.6025</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6026,7 +6034,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
+          <t>0x23b0d4e53469f4f65c8f42b41714ef77f1b09682ff2e352bb7f94995a0223dcb</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6056,7 +6064,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785734506</t>
+          <t>1785734664</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6066,7 +6074,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13.029412</t>
+          <t>353.609942</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6083,62 +6091,54 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
+          <t>0x457bc29d6a031eaca79d2a4ed381dae34885d77a3f580fb5b47facba8f815fcd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x960070fC76573ff9c086dB473f99CA99ea914dd6</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19.5311</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.0675</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Celtic vs Dundee FC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Dundee FC</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Celtic vs Dundee FC</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Celtic</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Dundee FC</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
+          <t>0x273964ed369eb86868634579e67e9aae203a47322e33fd319171ec517c9cdcb5</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785727225</t>
+          <t>1785734506</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>289.34963</t>
+          <t>13.029412</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6195,23 +6195,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
+          <t>0x8dfe6b3c520c9f7ccd81f0bc11591b70428bc4fea981d23c82aa1bfdf0eb2fbf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xA44AB2Cf43d5D82896598FF80855897B50aC323A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>19.5311</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0675</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6219,7 +6223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dundee FC</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6227,27 +6235,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>Celtic vs Dundee FC</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee FC</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x80818116cd3d437b09b855f8b3c980ad1aecbbde9ec881abbe8897ca18c95169</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228045</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6272,17 +6280,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785682854</t>
+          <t>1785727225</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785781800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>324.0</t>
+          <t>289.34963</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6299,7 +6307,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
+          <t>0x7a2e4070d6edeeb27d35ed976f9dc0f848cfc03ee2d8617640f48a3e7e28fd90</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6310,7 +6318,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6376,7 +6384,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785682817</t>
+          <t>1785682854</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6386,7 +6394,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>324.0</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6403,7 +6411,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
+          <t>0xb8482a3d708af9f66e6cc7fe703066b55c942fe470fed9b6263c1722629b25c9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6411,19 +6419,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4937</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6431,26 +6435,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785682785</t>
+          <t>1785682817</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>31.635443</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6515,23 +6515,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
+          <t>0x8262e8f0cf74fd9015345f50f9be5be4821b6faf1753965a5d474e6baf7cc80b</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>93.10524</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.4937</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6539,7 +6543,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -6562,7 +6570,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6592,7 +6600,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785682784</t>
+          <t>1785682785</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6602,7 +6610,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>122.105233</t>
+          <t>31.635443</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6619,7 +6627,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
+          <t>0xac9d9ab1a04e56373ad550c2747676870ab770fce067f4cd330a8df4f53ca200</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6630,12 +6638,12 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>98.4284</t>
+          <t>93.10524</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7612</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6696,7 +6704,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785682781</t>
+          <t>1785682784</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6706,7 +6714,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>129.298391</t>
+          <t>122.105233</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6723,18 +6731,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
+          <t>0x2e8e4d5b3299149ee8c734304817e0e27c746c4d03bc568a40165844be1f50b3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>98.4284</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6800,7 +6808,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785682739</t>
+          <t>1785682781</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6810,7 +6818,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>6.568131</t>
+          <t>129.298391</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6827,18 +6835,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
+          <t>0x4ebb12d579602e5e7408f41b99700b42aa2356b057582b282d958fd5043d5a23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19.4816</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6904,7 +6912,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785682735</t>
+          <t>1785682739</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6914,7 +6922,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>25.591593</t>
+          <t>6.568131</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,18 +6939,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
+          <t>0x56a7806404fc86f3c3d446405c2fadfb72b58fcac6eaa98379418ee902316efd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.60848</t>
+          <t>19.4816</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7008,7 +7016,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785682733</t>
+          <t>1785682735</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7018,7 +7026,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>6.053833</t>
+          <t>25.591593</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7035,18 +7043,18 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
+          <t>0xe9d33c25c2f1e3107663188dece6970b086a2f190fee38648c8aa30c262a6dd6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>92.46597</t>
+          <t>4.60848</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7112,7 +7120,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785681750</t>
+          <t>1785682733</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7122,7 +7130,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>121.46597</t>
+          <t>6.053833</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7139,28 +7147,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
+          <t>0x20b6cfa49a80ab404ef3332b9e22ad9e6743a3d2e3a35be6c51bc46058cdc63c</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>32.47659</t>
+          <t>92.46597</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (6.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7171,27 +7179,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7216,17 +7224,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785681479</t>
+          <t>1785681750</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>61.276585</t>
+          <t>121.46597</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7243,28 +7251,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
+          <t>0x6738d383597a79e14e2c4e9973e2df19a3517634899f779deee2f389dc23b1b6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>32.47659</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (6.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7275,27 +7283,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x33ee970490c6042db27ebfaf01f9feb7428754c09faa00f2f34b5eab91c93bc2</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7320,17 +7328,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785680616</t>
+          <t>1785681479</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>47.446301</t>
+          <t>61.276585</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,28 +7355,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
+          <t>0x19512362a81c98663ad74bd062eca9589e6290edbdbc7038df49a64ef6b25922</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>139.68586</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3413</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Premiership</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7394,7 +7402,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7424,7 +7432,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785680329</t>
+          <t>1785680616</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7434,7 +7442,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>409.335853</t>
+          <t>47.446301</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,7 +7459,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
+          <t>0xcf306667a94f5225ee0154ca6f2fd2f255e23e66d77b59396c7dc3be23071806</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7462,17 +7470,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>122.41894</t>
+          <t>139.68586</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1.3413</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7498,7 +7506,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x7368e5991b4a28819404d360845838f26a1d00630406708bce6228fbc692b904</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7538,7 +7546,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>233.178933</t>
+          <t>409.335853</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7555,23 +7563,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
+          <t>0xadae641fe60f290c87c17620a8cb7c4209223a85a9bb6e7adbcb65f77230dcbc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>122.41894</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.525</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7602,7 +7610,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7632,7 +7640,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785680318</t>
+          <t>1785680329</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7642,7 +7650,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.34002</t>
+          <t>233.178933</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,7 +7667,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
+          <t>0xf7ff10636d52f446c01c4fd752311b181a46c868f923ee782c336d341299b82e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7670,12 +7678,12 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>168.68</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7388</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7736,7 +7744,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785680305</t>
+          <t>1785680318</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7746,7 +7754,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>228.331641</t>
+          <t>1.34002</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7763,7 +7771,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
+          <t>0xa3c04dcdbb337e2997d230cf027e889b0a4dad03c71262d41c5201660c18c4fa</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7774,12 +7782,12 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>168.68</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7388</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7840,7 +7848,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785678530</t>
+          <t>1785680305</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7850,7 +7858,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>27.667233</t>
+          <t>228.331641</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,7 +7875,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
+          <t>0x3968858a0e69daf1305cd712f45a36940283aa140fc8b740fd60d8987e6bb62d</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7878,7 +7886,7 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>46.31885</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7944,7 +7952,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785678083</t>
+          <t>1785678530</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7954,7 +7962,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>62.911851</t>
+          <t>27.667233</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7971,7 +7979,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
+          <t>0x675684d4032052fc1f6f62fe51a03d5bcebe51a3b03abb03fadb2807d24f7a4f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7982,12 +7990,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>40.66999</t>
+          <t>46.31885</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8048,7 +8056,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785677996</t>
+          <t>1785678083</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8058,7 +8066,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>55.33332</t>
+          <t>62.911851</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,7 +8083,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
+          <t>0x9afb5980ba1cb57f842711e14624569d55fc99e590e14f1cb96ed3f784321c00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8086,7 +8094,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12.42999</t>
+          <t>40.66999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8152,7 +8160,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785677920</t>
+          <t>1785677996</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8162,7 +8170,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>16.911551</t>
+          <t>55.33332</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8179,7 +8187,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
+          <t>0x9baa784cbcc19408f3c8011d0adeefb4a5916731c9d8474770f73ec21d176dc4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8190,7 +8198,7 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.12999</t>
+          <t>12.42999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8256,7 +8264,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785677881</t>
+          <t>1785677920</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8266,7 +8274,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.537401</t>
+          <t>16.911551</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8283,7 +8291,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
+          <t>0xe9d12eb96dfe5ee8ff695e774ac2ad10b0c735d8690f9e46ceed9deb9b75bee5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8291,19 +8299,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1.12999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.735</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8311,11 +8315,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785677338</t>
+          <t>1785677881</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>39.154185</t>
+          <t>1.537401</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8395,12 +8395,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
+          <t>0xfaa2fb101d3e0869eaa3ac757c4f7fc3ecdb870c6880e5e41af90fadceeeed92</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8410,22 +8410,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>55.11998</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785677298</t>
+          <t>1785677338</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>73.86262</t>
+          <t>39.154185</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8507,12 +8507,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
+          <t>0xe1d07fe999d66f522e456e3e1410e2e5c1275339a47fa200f00064acde1a858c</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8522,22 +8522,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>55.11998</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x6f1421cf1471e2231af6c849487f42f5fcb41e0711c892698154b4de185c87bc</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785675836</t>
+          <t>1785677298</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>4.546256</t>
+          <t>73.86262</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
+          <t>0x6a98784424708b7f764b3e56f605a829365df81be315b110c013326e0d6618bd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785675803</t>
+          <t>1785675836</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>9.057269</t>
+          <t>4.546256</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
+          <t>0xe17d5b7e60ad6d80a73ac0770196a8066d6d6df25df7254c6c981ff460fcc7e0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785673389</t>
+          <t>1785675803</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>3.524229</t>
+          <t>9.057269</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8843,7 +8843,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
+          <t>0xe13cbe68d39169a6f5124e8e7b52b9ec07952d612e056133b985375c8ba7371b</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8851,15 +8851,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8867,7 +8871,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -8890,7 +8898,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8930,7 +8938,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>3.757303</t>
+          <t>3.524229</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8947,7 +8955,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
+          <t>0x19cec2da220cb59967bef03dd50dabc93a8fccca1da23e6801cc5d08f650c4fc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8955,19 +8963,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.2837</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8975,11 +8979,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785672902</t>
+          <t>1785673389</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>59.806167</t>
+          <t>3.757303</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
+          <t>0x038083a254cb019ba4c27bf1ad417f6020a205d47f1a20b064c8e9186960415f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9074,22 +9074,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.2837</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9099,27 +9099,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0xe77cfc56ee744f9f462860352a16ae0129b82cd6629eba7d646299aa85dd7a11</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9144,17 +9144,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785672780</t>
+          <t>1785672902</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>20.675676</t>
+          <t>59.806167</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9171,31 +9171,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
+          <t>0xef7e73ff56c4102671b7bd2f6b234e11048259ebaa8f08fdcc16ae430cdcbfd7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9203,27 +9211,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9248,17 +9256,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785672554</t>
+          <t>1785672780</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>20.675676</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9275,23 +9283,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
+          <t>0x8dc8895814970c56665513f993547d6aec6abb7bdc63e5f2e794e4fa24c48364</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>29.66982</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9352,7 +9360,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785672525</t>
+          <t>1785672554</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9362,7 +9370,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>53.57981</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9379,27 +9387,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
+          <t>0xf3e9fddffc26b36245960c7e039ab617a2e1c026bc2a47216cf1eec62829d647</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29.66982</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9407,11 +9411,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>St. Johnstone</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9419,27 +9419,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9464,17 +9464,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785670003</t>
+          <t>1785672525</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>11.461318</t>
+          <t>53.57981</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
+          <t>0x11bed46c6f39d20ac8fe72871e0191b7bbb801a84e322ed5ebcebf9c602b7771</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785670001</t>
+          <t>1785670003</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9603,12 +9603,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
+          <t>0xeccb86be944315a93d3b88ae41fd25d9a7b2ac817aee46c6a7339bcee734ed41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785669973</t>
+          <t>1785670001</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>51.310345</t>
+          <t>11.461318</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9715,7 +9715,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
+          <t>0xf44cadfbddefb7a862fb300e7dc4d967c6b5fbf5f54d356abce4b5efba86d382</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>137.535817</t>
+          <t>51.310345</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9827,23 +9827,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
+          <t>0xcce1a456cad70096247bae729ae9c14503f2e1f5512a3868e2d1e0e14b1590da</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9851,7 +9855,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>St. Johnstone</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -9859,27 +9867,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0xd3c447d424abdf1a0f224ade57ee134329e58b50bab063442ee3def361a56544</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9904,17 +9912,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785669518</t>
+          <t>1785669973</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>137.535817</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9931,7 +9939,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
+          <t>0x049f125ebf216fb6c62de93592e1ddde259ec4d1d605f3869262601c2cebe572</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9939,19 +9947,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9959,26 +9963,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785669517</t>
+          <t>1785669518</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>150.898876</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10043,7 +10043,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
+          <t>0x302b1ae856cc1e550fa7fce324e700707d997269e409a1c09dcaf6a12c4eb819</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10051,15 +10051,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8.71999</t>
+          <t>67.15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10067,7 +10071,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -10090,7 +10098,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10120,7 +10128,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785668506</t>
+          <t>1785669517</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10130,7 +10138,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>11.986241</t>
+          <t>150.898876</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10147,7 +10155,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
+          <t>0x26f82279874cfc55afa069fc68a4c07436f75d799a78b014e4a213a8c557db6b</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10158,7 +10166,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>8.71999</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10224,7 +10232,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785668484</t>
+          <t>1785668506</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10234,7 +10242,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>117.429553</t>
+          <t>11.986241</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10251,7 +10259,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
+          <t>0x8abf01c155f552f6bf1c46549d2c8807d7d02092f873f2ca66ce17345d0a6478</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10262,12 +10270,12 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10328,7 +10336,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785668374</t>
+          <t>1785668484</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10338,7 +10346,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>68.97074</t>
+          <t>117.429553</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10355,7 +10363,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
+          <t>0xce5d9f85853f19e69328a151526617e11ef5dad178ea5280314f9397ada4ba38</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10366,12 +10374,12 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>50.09205</t>
+          <t>50.09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10442,7 +10450,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>68.855052</t>
+          <t>68.97074</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10459,7 +10467,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
+          <t>0x3f59698b8f045fefcc616afdcb7cfdd72f20922050102c3655904ef16179cb34</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10470,7 +10478,7 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>50.09205</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10536,7 +10544,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785668313</t>
+          <t>1785668374</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10546,7 +10554,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>68.855052</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,7 +10571,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
+          <t>0xce7192eddb422335f4d2d93b513d6a9058c45bb3dd0d674975d037dc899ff493</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10574,12 +10582,12 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10640,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785668312</t>
+          <t>1785668313</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10650,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>113.239243</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10667,7 +10675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
+          <t>0x3884bc12f10cc16d69593c0570d7b80349f03c4ee756e6dba5b992ac23d07d49</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10678,12 +10686,12 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>82.24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10744,7 +10752,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785668199</t>
+          <t>1785668312</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10754,7 +10762,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>13.745691</t>
+          <t>113.239243</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10771,7 +10779,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
+          <t>0xefabca8848fe24489a8e882834b864ed3690ca44b2c083f9b5ecb8e3bf207594</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10782,12 +10790,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>73.13</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10848,7 +10856,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785668198</t>
+          <t>1785668199</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10858,7 +10866,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>100.695353</t>
+          <t>13.745691</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10875,7 +10883,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
+          <t>0x5c32b5bcbf5526217b3d3937153aa291ab5c660256ef92d941d17dcfe5ebff15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10886,7 +10894,7 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>73.13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10952,7 +10960,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785668128</t>
+          <t>1785668198</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10962,7 +10970,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>16.192771</t>
+          <t>100.695353</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10979,7 +10987,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
+          <t>0x53c10e66b52b042a10b1b270b3eeb1f4413004fbf9b0e04de27cb82718c5a0fc</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10990,12 +10998,12 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>9.99796</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11056,7 +11064,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785668096</t>
+          <t>1785668128</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11066,7 +11074,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>13.7429</t>
+          <t>16.192771</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11083,7 +11091,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
+          <t>0x390eb3d0a3d1bce4612efc9c932edab6a9b59f953bbcd1ce7987cc2c73ec0258</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11094,12 +11102,12 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.99796</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.7262</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11160,7 +11168,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785668095</t>
+          <t>1785668096</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11170,7 +11178,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>13.769363</t>
+          <t>13.7429</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11187,7 +11195,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
+          <t>0x45bcd96ec9899ad76886d4a24bfb86b7a483d3579582556aec2d65bf721c75b1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11198,7 +11206,7 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21.08999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11264,7 +11272,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785668039</t>
+          <t>1785668095</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11274,7 +11282,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>29.039573</t>
+          <t>13.769363</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11291,27 +11299,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
+          <t>0xea5bc15ea9ac79396b3c40f709463b65ee45ed4471b73994e7298c874892113b</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>21.08999</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.7262</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11319,26 +11323,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Hibernian vs Motherwell</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>Hibernian</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Hibernian vs Motherwell</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>Motherwell</t>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0x06c9c9cb7ee96efa336cd73a5409afd448f3d5029a1f440fa11efc8f8af0de84</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785662110</t>
+          <t>1785668039</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>51.213675</t>
+          <t>29.039573</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11403,23 +11403,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
+          <t>0xa3246839c82e1d3b7b79ec7134f5e16ac34c978224c73f9cf936402bb3f46246</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>0x3c0287d63932634992dC40382ee8C4Fa83681Dd1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>39.80897</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11427,7 +11431,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11435,27 +11443,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -11480,17 +11488,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785660888</t>
+          <t>1785662110</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>56.068972</t>
+          <t>51.213675</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11507,27 +11515,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
+          <t>0x1d1e098954f1c91c97a06acd702caf64f5c976927b5cfeaca5e2eb798a33b4e4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>39.80897</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.4387</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11535,11 +11539,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Hibernian</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11547,27 +11547,27 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
+          <t>0xbebf21a64fc9e69fed2003bb3aaf7e9db7162dbf82e179c3e21769683becd2a1</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -11592,17 +11592,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1785659879</t>
+          <t>1785660888</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>4.672365</t>
+          <t>56.068972</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11619,59 +11619,67 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
+          <t>0x3a91b4ee4ebe4a44ecdf84e9d6ea4e3c65ba8af4f7422c11d076afba8bf5a45e</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.4287</t>
+          <t>1.4387</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
+          <t>0x9f1a3561e16a2d0b3c37f6e3c72434f322dfbe1a4e4f2db43c4834fec7e37ca8</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -11696,17 +11704,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1785656458</t>
+          <t>1785659879</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>11.03207</t>
+          <t>4.672365</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11723,7 +11731,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
+          <t>0xd47a15b073a363789220e1cf024b7af5305a66f3777fd0039ee12d3de57bd0bf</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11734,7 +11742,7 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11800,7 +11808,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1785656419</t>
+          <t>1785656458</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11810,7 +11818,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2.425656</t>
+          <t>11.03207</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11827,7 +11835,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
+          <t>0x941e76d7a6a1b26012f4ee31714ecadb8a2a95b32d0be17fbc02b0a5582a1d62</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11838,17 +11846,17 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.4287</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -11874,7 +11882,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
+          <t>0x36bed9ba7cf9a4329b968ce6013308ee218af06f4b67ca9e7013eca5c9631d79</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11904,7 +11912,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1785636203</t>
+          <t>1785656419</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11914,7 +11922,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1.574803</t>
+          <t>2.425656</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11931,7 +11939,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
+          <t>0x75ef518b65fe522ded9c78a1d5f31a90d2901382f170023f7b6dd2d74fefc9ff</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11939,31 +11947,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -11971,27 +11971,27 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Hibernian vs Motherwell</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
+          <t>0x53a71c3f6c6ea99c0a39f725804b4ea70d4a29654a2903d942ccfb92e2bcd5c3</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>L19228046</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -12016,17 +12016,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1785635973</t>
+          <t>1785636203</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>1785684600</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>20.356234</t>
+          <t>1.574803</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
+          <t>0x828cc7a1897c5fc5bc4301f9a7440aeda6cda8fac90ae0bd1c98ee5719a0f76e</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12058,12 +12058,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1785630118</t>
+          <t>1785635973</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>7.175258</t>
+          <t>20.356234</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12155,7 +12155,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
+          <t>0x6ab196073a2c34a857b463177bac529748ff13ee57f0aec52e6f6fc643ae0718</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12163,23 +12163,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.7225</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12187,27 +12195,27 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Kilmarnock</t>
+          <t>Hibernian vs Motherwell</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
+          <t>0x2783261fcb8854d285b611657288b8d77bcc8e0dfdcc94b3e12d815b0c6f0ad1</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>L19228040</t>
+          <t>L19228046</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -12232,17 +12240,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1785623149</t>
+          <t>1785630118</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>1785675600</t>
+          <t>1785684600</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>3.847751</t>
+          <t>7.175258</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12259,39 +12267,31 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
+          <t>0x119739feb921ac6aaf1c73d753c84fe8b4ef7a1d89b8d653c384bcb65d17eb44</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>540.4</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.7225</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12299,27 +12299,27 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
+          <t>St. Johnstone vs Kilmarnock</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x23b587c4d4eadaf253c4b86c75fcdd4ec70729ea8567febc472ad12253b9fe16</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>L19228039</t>
+          <t>L19228040</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -12344,17 +12344,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1785606461</t>
+          <t>1785623149</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>1785601800</t>
+          <t>1785675600</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1228.181818</t>
+          <t>3.847751</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12371,12 +12371,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
+          <t>0x285a5fd104f5d7656de510897faa7bd4458d7a455cf677dfe51254fe7ba4d2b6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>540.4</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.3225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1785606213</t>
+          <t>1785606461</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>15.503876</t>
+          <t>1228.181818</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12483,12 +12483,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
+          <t>0xf22ffe2952c7c68f8dfc9f2d67c7abc2524fa132087e243d33ec3a6cc341bd65</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12498,39 +12498,39 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.0938</t>
+          <t>1.3225</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0xe60c02a40f6d793a7b64339680c7a119b47f886321c3addc85f497e35e0ca793</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1785606061</t>
+          <t>1785606213</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>173.44</t>
+          <t>15.503876</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12595,7 +12595,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
+          <t>0x59fde39b6f148fd1215b657887ed4f43e9a2db36d1798dda0c37e8dfc7fbde76</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12610,22 +12610,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0938</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1785606042</t>
+          <t>1785606061</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>218.454545</t>
+          <t>173.44</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12707,7 +12707,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
+          <t>0x0e430f6a34ae833d3b326cdb6db44835894df5a80a68df992f04a51a1fbcede8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12722,39 +12722,39 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>113.82262</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.0962</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1785605997</t>
+          <t>1785606042</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1182.572675</t>
+          <t>218.454545</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12819,7 +12819,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
+          <t>0xe2f524ccfb2b8ea547b7f17ddfbd89a1865cfb986eb6bc2ce1ce4630f8388d54</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12827,23 +12827,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>111.28764</t>
+          <t>113.82262</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0962</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Premiership</t>
@@ -12866,7 +12874,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -12896,7 +12904,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1785604719</t>
+          <t>1785605997</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12906,7 +12914,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>227.117633</t>
+          <t>1182.572675</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -12923,62 +12931,54 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
+          <t>0x798a2dd92705725f7e43da661a6058835f408eb6bcf6cdf2ebadab6d345eb3a1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>111.28764</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Premiership</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Heart of Midlothian</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
+          <t>0x28b154cd868e90e22afd88e0b88b37d60f306ff33bf341cfb50e3c409aac81a7</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1785604200</t>
+          <t>1785604719</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1.459854</t>
+          <t>227.117633</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13035,12 +13035,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
+          <t>0x848d8d806be9a756592c44678cf4f627ba77b9010fc492c9e3dd32942dc0bff2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x07708a791d2c7549244E6c62A14B12b09FAAE65D</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1785604180</t>
+          <t>1785604200</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>3.591241</t>
+          <t>1.459854</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13147,12 +13147,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
+          <t>0x925930e535ba2a3cd4d63099999c84a9977750e4607d4f1e3b8f69af1a5bae17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13162,39 +13162,39 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>Premiership</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Aberdeen vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>Aberdeen</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Premiership</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Aberdeen vs Heart of Midlothian</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Aberdeen</t>
-        </is>
-      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>Heart of Midlothian</t>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
+          <t>0x0744485ec0f21d4fce373018d4739c77bf4d61e274d73317a5bbfda23f87f48b</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1785604028</t>
+          <t>1785604180</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>147.857143</t>
+          <t>3.591241</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13259,7 +13259,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
+          <t>0x4c6a1fd994bbc9b3204ba07f5a25d6d9b2fadcb5868fde25397da4c34af10eec</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Premiership</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec424b47239b43b6</t>
+          <t>0x13afa08855879d0fb10ba39752b59dd3851c9a86db3e7d49dcd53265c0a094b8</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1785604011</t>
+          <t>1785604028</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>549.929412</t>
+          <t>147.857143</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0xcf645932fc9fc44dcce78623fe36e0b5a2a770c7768c166ded87f80ea4629ad0</t>
+          <t>0x4840850d5a78e921d1d523868aea7485202701a718ec2e7aa0c19b9b4dc54a39</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -13386,22 +13386,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1142.73999</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>0x348e726f6237441e04fb457f50aef2158e209f96c9abe9cde51d535052b0a0ef</t>
+          <t>0x62d76eb778a6607a159e32d82b64cfbf512384b97ecae550ec4